--- a/data/out/test0/seikyuusyo202505_Python版_2pt.xlsx
+++ b/data/out/test0/seikyuusyo202505_Python版_2pt.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,8 +57,32 @@
       <sz val="8.6"/>
     </font>
     <font>
+      <name val="MS Mincho"/>
+      <sz val="11.5"/>
+    </font>
+    <font>
+      <name val="MS PGothic"/>
+      <sz val="6.5"/>
+    </font>
+    <font>
+      <name val="MS PGothic"/>
+      <sz val="7.9"/>
+    </font>
+    <font>
+      <name val="MS PGothic"/>
+      <sz val="7"/>
+    </font>
+    <font>
       <name val="MS Gothic"/>
       <sz val="6"/>
+    </font>
+    <font>
+      <name val="MS PMincho"/>
+      <sz val="5.1"/>
+    </font>
+    <font>
+      <name val="MS PMincho"/>
+      <sz val="7.6"/>
     </font>
   </fonts>
   <fills count="2">
@@ -147,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -175,34 +199,73 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -666,7 +729,7 @@
       <c r="AJ6" s="2"/>
       <c r="AK6" s="2"/>
       <c r="AL6" s="2"/>
-      <c r="AM6" s="12" t="inlineStr">
+      <c r="AM6" s="13" t="inlineStr">
         <is>
           <t>－</t>
         </is>
@@ -680,35 +743,35 @@
       <c r="AT6" s="3"/>
     </row>
     <row r="7">
-      <c r="AF7" s="13" t="inlineStr">
+      <c r="AF7" s="14" t="inlineStr">
         <is>
           <t>住</t>
         </is>
       </c>
-      <c r="AJ7" s="14" t="inlineStr">
+      <c r="AJ7" s="15" t="inlineStr">
         <is>
           <t>所</t>
         </is>
       </c>
-      <c r="AT7" s="15"/>
+      <c r="AT7" s="16"/>
     </row>
     <row r="8">
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>支払票NO</t>
         </is>
       </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="18"/>
-      <c r="AF8" s="13" t="inlineStr">
+      <c r="C8" s="18"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="19"/>
+      <c r="AF8" s="14" t="inlineStr">
         <is>
           <t>取引先名</t>
         </is>
       </c>
-      <c r="AT8" s="15"/>
+      <c r="AT8" s="16"/>
     </row>
     <row r="9">
       <c r="B9" s="9" t="inlineStr">
@@ -716,17 +779,17 @@
           <t>※請求書ご提出にあたってのお願い</t>
         </is>
       </c>
-      <c r="AF9" s="13" t="inlineStr">
+      <c r="AF9" s="14" t="inlineStr">
         <is>
           <t>代表者名</t>
         </is>
       </c>
-      <c r="AS9" s="14" t="inlineStr">
+      <c r="AS9" s="21" t="inlineStr">
         <is>
           <t>印</t>
         </is>
       </c>
-      <c r="AT9" s="15"/>
+      <c r="AT9" s="16"/>
     </row>
     <row r="10">
       <c r="B10" s="9" t="inlineStr">
@@ -749,23 +812,23 @@
           <t>太枠内と灰色の部分</t>
         </is>
       </c>
-      <c r="AF10" s="20"/>
-      <c r="AJ10" s="14" t="inlineStr">
+      <c r="AF10" s="22"/>
+      <c r="AJ10" s="9" t="inlineStr">
         <is>
           <t>電話FAX</t>
         </is>
       </c>
-      <c r="AN10" s="14" t="inlineStr">
+      <c r="AN10" s="9" t="inlineStr">
         <is>
           <t>－－</t>
         </is>
       </c>
-      <c r="AQ10" s="14" t="inlineStr">
+      <c r="AQ10" s="9" t="inlineStr">
         <is>
           <t>－－</t>
         </is>
       </c>
-      <c r="AT10" s="15"/>
+      <c r="AT10" s="16"/>
     </row>
     <row r="11">
       <c r="E11" s="9" t="inlineStr">
@@ -778,12 +841,12 @@
           <t>太枠内のみ</t>
         </is>
       </c>
-      <c r="AF11" s="13" t="inlineStr">
+      <c r="AF11" s="14" t="inlineStr">
         <is>
           <t>登録番号Ｔ</t>
         </is>
       </c>
-      <c r="AT11" s="15"/>
+      <c r="AT11" s="16"/>
     </row>
     <row r="12">
       <c r="B12" s="9" t="inlineStr">
@@ -791,7 +854,7 @@
           <t>２．納入品目を記入しきれない場合は、総額を記入し御社の請求明細書を添付してください。</t>
         </is>
       </c>
-      <c r="AF12" s="21" t="inlineStr">
+      <c r="AF12" s="23" t="inlineStr">
         <is>
           <t>振込先情報</t>
         </is>
@@ -801,14 +864,14 @@
       <c r="AI12" s="6"/>
       <c r="AJ12" s="6"/>
       <c r="AK12" s="6"/>
-      <c r="AL12" s="22" t="inlineStr">
+      <c r="AL12" s="24" t="inlineStr">
         <is>
           <t>銀行預金</t>
         </is>
       </c>
       <c r="AM12" s="6"/>
       <c r="AN12" s="6"/>
-      <c r="AO12" s="22" t="inlineStr">
+      <c r="AO12" s="25" t="inlineStr">
         <is>
           <t>口座番号：支店</t>
         </is>
@@ -820,16 +883,16 @@
       <c r="AT12" s="7"/>
     </row>
     <row r="13">
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>３．軽油税、産廃税については、「工事名（品名）」欄に個別に明記してください。</t>
         </is>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="3"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="18"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="19"/>
       <c r="H13" s="1"/>
       <c r="I13" s="2"/>
       <c r="J13" s="3"/>
@@ -858,54 +921,54 @@
       <c r="AG13" s="2"/>
       <c r="AH13" s="2"/>
       <c r="AI13" s="3"/>
-      <c r="AJ13" s="16" t="inlineStr">
+      <c r="AJ13" s="17" t="inlineStr">
         <is>
           <t>口座名義(ｶﾀｶﾅ)：</t>
         </is>
       </c>
-      <c r="AK13" s="17"/>
-      <c r="AL13" s="17"/>
-      <c r="AM13" s="17"/>
-      <c r="AN13" s="17"/>
-      <c r="AO13" s="17"/>
-      <c r="AP13" s="17"/>
-      <c r="AQ13" s="17"/>
-      <c r="AR13" s="18"/>
+      <c r="AK13" s="18"/>
+      <c r="AL13" s="18"/>
+      <c r="AM13" s="18"/>
+      <c r="AN13" s="18"/>
+      <c r="AO13" s="18"/>
+      <c r="AP13" s="18"/>
+      <c r="AQ13" s="18"/>
+      <c r="AR13" s="19"/>
       <c r="AS13" s="1"/>
       <c r="AT13" s="3"/>
     </row>
     <row r="14">
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="27" t="inlineStr">
         <is>
           <t>工事NO</t>
         </is>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="7"/>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="28" t="inlineStr">
         <is>
           <t>科目コード</t>
         </is>
       </c>
-      <c r="F14" s="14" t="inlineStr">
+      <c r="F14" s="28" t="inlineStr">
         <is>
           <t>科目名</t>
         </is>
       </c>
-      <c r="H14" s="24"/>
-      <c r="I14" s="22" t="inlineStr">
+      <c r="H14" s="29"/>
+      <c r="I14" s="30" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
       <c r="J14" s="7"/>
-      <c r="K14" s="24"/>
+      <c r="K14" s="29"/>
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
       <c r="O14" s="6"/>
       <c r="P14" s="6"/>
-      <c r="Q14" s="22" t="inlineStr">
+      <c r="Q14" s="30" t="inlineStr">
         <is>
           <t>工事名（品名）</t>
         </is>
@@ -918,13 +981,13 @@
       <c r="W14" s="6"/>
       <c r="X14" s="6"/>
       <c r="Y14" s="7"/>
-      <c r="Z14" s="21" t="inlineStr">
+      <c r="Z14" s="31" t="inlineStr">
         <is>
           <t>内訳NO</t>
         </is>
       </c>
       <c r="AA14" s="7"/>
-      <c r="AB14" s="21" t="inlineStr">
+      <c r="AB14" s="27" t="inlineStr">
         <is>
           <t>現在注文金額</t>
         </is>
@@ -932,7 +995,7 @@
       <c r="AC14" s="6"/>
       <c r="AD14" s="6"/>
       <c r="AE14" s="7"/>
-      <c r="AF14" s="21" t="inlineStr">
+      <c r="AF14" s="27" t="inlineStr">
         <is>
           <t>前回迄の支払額</t>
         </is>
@@ -940,20 +1003,20 @@
       <c r="AG14" s="6"/>
       <c r="AH14" s="6"/>
       <c r="AI14" s="7"/>
-      <c r="AJ14" s="19"/>
-      <c r="AK14" s="17"/>
-      <c r="AL14" s="17"/>
-      <c r="AM14" s="25" t="inlineStr">
+      <c r="AJ14" s="20"/>
+      <c r="AK14" s="18"/>
+      <c r="AL14" s="18"/>
+      <c r="AM14" s="32" t="inlineStr">
         <is>
           <t>今回請求額</t>
         </is>
       </c>
-      <c r="AN14" s="17"/>
-      <c r="AO14" s="18"/>
-      <c r="AP14" s="19"/>
-      <c r="AQ14" s="17"/>
-      <c r="AR14" s="18"/>
-      <c r="AS14" s="21" t="inlineStr">
+      <c r="AN14" s="18"/>
+      <c r="AO14" s="19"/>
+      <c r="AP14" s="20"/>
+      <c r="AQ14" s="18"/>
+      <c r="AR14" s="19"/>
+      <c r="AS14" s="33" t="inlineStr">
         <is>
           <t>グリーン産業</t>
         </is>
@@ -961,168 +1024,168 @@
       <c r="AT14" s="7"/>
     </row>
     <row r="15">
-      <c r="B15" s="19"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
-      <c r="N15" s="17"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="17"/>
-      <c r="Q15" s="17"/>
-      <c r="R15" s="17"/>
-      <c r="S15" s="17"/>
-      <c r="T15" s="17"/>
-      <c r="U15" s="17"/>
-      <c r="V15" s="17"/>
-      <c r="W15" s="17"/>
-      <c r="X15" s="17"/>
-      <c r="Y15" s="18"/>
-      <c r="Z15" s="19"/>
-      <c r="AA15" s="18"/>
-      <c r="AB15" s="16" t="inlineStr">
+      <c r="B15" s="20"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="18"/>
+      <c r="M15" s="18"/>
+      <c r="N15" s="18"/>
+      <c r="O15" s="18"/>
+      <c r="P15" s="18"/>
+      <c r="Q15" s="18"/>
+      <c r="R15" s="18"/>
+      <c r="S15" s="18"/>
+      <c r="T15" s="18"/>
+      <c r="U15" s="18"/>
+      <c r="V15" s="18"/>
+      <c r="W15" s="18"/>
+      <c r="X15" s="18"/>
+      <c r="Y15" s="19"/>
+      <c r="Z15" s="20"/>
+      <c r="AA15" s="19"/>
+      <c r="AB15" s="34" t="inlineStr">
         <is>
           <t>（税抜金額）</t>
         </is>
       </c>
-      <c r="AC15" s="17"/>
-      <c r="AD15" s="17"/>
-      <c r="AE15" s="18"/>
-      <c r="AF15" s="19"/>
-      <c r="AG15" s="25" t="inlineStr">
+      <c r="AC15" s="18"/>
+      <c r="AD15" s="18"/>
+      <c r="AE15" s="19"/>
+      <c r="AF15" s="20"/>
+      <c r="AG15" s="35" t="inlineStr">
         <is>
           <t>（税抜金額）</t>
         </is>
       </c>
-      <c r="AH15" s="17"/>
-      <c r="AI15" s="18"/>
-      <c r="AJ15" s="14" t="inlineStr">
+      <c r="AH15" s="18"/>
+      <c r="AI15" s="19"/>
+      <c r="AJ15" s="36" t="inlineStr">
         <is>
           <t>（税抜金額）</t>
         </is>
       </c>
-      <c r="AL15" s="14" t="inlineStr">
+      <c r="AL15" s="10" t="inlineStr">
         <is>
           <t>（税抜金額）</t>
         </is>
       </c>
-      <c r="AP15" s="14" t="inlineStr">
+      <c r="AP15" s="36" t="inlineStr">
         <is>
           <t>税率</t>
         </is>
       </c>
-      <c r="AQ15" s="14" t="inlineStr">
+      <c r="AQ15" s="10" t="inlineStr">
         <is>
           <t>税率</t>
         </is>
       </c>
-      <c r="AS15" s="19"/>
-      <c r="AT15" s="18"/>
+      <c r="AS15" s="20"/>
+      <c r="AT15" s="19"/>
     </row>
     <row r="16">
-      <c r="AJ16" s="19"/>
-      <c r="AK16" s="17"/>
-      <c r="AL16" s="17"/>
-      <c r="AM16" s="17"/>
-      <c r="AN16" s="17"/>
-      <c r="AO16" s="18"/>
-      <c r="AP16" s="19"/>
-      <c r="AQ16" s="17"/>
-      <c r="AR16" s="18"/>
+      <c r="AJ16" s="20"/>
+      <c r="AK16" s="18"/>
+      <c r="AL16" s="18"/>
+      <c r="AM16" s="18"/>
+      <c r="AN16" s="18"/>
+      <c r="AO16" s="19"/>
+      <c r="AP16" s="20"/>
+      <c r="AQ16" s="18"/>
+      <c r="AR16" s="19"/>
     </row>
     <row r="17">
-      <c r="B17" s="19"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="17"/>
-      <c r="M17" s="17"/>
-      <c r="N17" s="17"/>
-      <c r="O17" s="17"/>
-      <c r="P17" s="17"/>
-      <c r="Q17" s="17"/>
-      <c r="R17" s="17"/>
-      <c r="S17" s="17"/>
-      <c r="T17" s="17"/>
-      <c r="U17" s="17"/>
-      <c r="V17" s="17"/>
-      <c r="W17" s="17"/>
-      <c r="X17" s="17"/>
-      <c r="Y17" s="18"/>
-      <c r="Z17" s="19"/>
-      <c r="AA17" s="18"/>
-      <c r="AB17" s="19"/>
-      <c r="AC17" s="17"/>
-      <c r="AD17" s="17"/>
-      <c r="AE17" s="18"/>
-      <c r="AF17" s="19"/>
-      <c r="AG17" s="17"/>
-      <c r="AH17" s="17"/>
-      <c r="AI17" s="18"/>
-      <c r="AS17" s="19"/>
-      <c r="AT17" s="18"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="18"/>
+      <c r="M17" s="18"/>
+      <c r="N17" s="18"/>
+      <c r="O17" s="18"/>
+      <c r="P17" s="18"/>
+      <c r="Q17" s="18"/>
+      <c r="R17" s="18"/>
+      <c r="S17" s="18"/>
+      <c r="T17" s="18"/>
+      <c r="U17" s="18"/>
+      <c r="V17" s="18"/>
+      <c r="W17" s="18"/>
+      <c r="X17" s="18"/>
+      <c r="Y17" s="19"/>
+      <c r="Z17" s="20"/>
+      <c r="AA17" s="19"/>
+      <c r="AB17" s="20"/>
+      <c r="AC17" s="18"/>
+      <c r="AD17" s="18"/>
+      <c r="AE17" s="19"/>
+      <c r="AF17" s="20"/>
+      <c r="AG17" s="18"/>
+      <c r="AH17" s="18"/>
+      <c r="AI17" s="19"/>
+      <c r="AS17" s="20"/>
+      <c r="AT17" s="19"/>
     </row>
     <row r="18">
-      <c r="AJ18" s="19"/>
-      <c r="AK18" s="17"/>
-      <c r="AL18" s="17"/>
-      <c r="AM18" s="17"/>
-      <c r="AN18" s="17"/>
-      <c r="AO18" s="18"/>
-      <c r="AP18" s="19"/>
-      <c r="AQ18" s="17"/>
-      <c r="AR18" s="18"/>
+      <c r="AJ18" s="20"/>
+      <c r="AK18" s="18"/>
+      <c r="AL18" s="18"/>
+      <c r="AM18" s="18"/>
+      <c r="AN18" s="18"/>
+      <c r="AO18" s="19"/>
+      <c r="AP18" s="20"/>
+      <c r="AQ18" s="18"/>
+      <c r="AR18" s="19"/>
     </row>
     <row r="19">
-      <c r="B19" s="19"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="18"/>
-      <c r="K19" s="19"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17"/>
-      <c r="N19" s="17"/>
-      <c r="O19" s="17"/>
-      <c r="P19" s="17"/>
-      <c r="Q19" s="17"/>
-      <c r="R19" s="17"/>
-      <c r="S19" s="17"/>
-      <c r="T19" s="17"/>
-      <c r="U19" s="17"/>
-      <c r="V19" s="17"/>
-      <c r="W19" s="17"/>
-      <c r="X19" s="17"/>
-      <c r="Y19" s="18"/>
-      <c r="Z19" s="19"/>
-      <c r="AA19" s="18"/>
-      <c r="AB19" s="19"/>
-      <c r="AC19" s="17"/>
-      <c r="AD19" s="17"/>
-      <c r="AE19" s="18"/>
-      <c r="AF19" s="19"/>
-      <c r="AG19" s="17"/>
-      <c r="AH19" s="17"/>
-      <c r="AI19" s="18"/>
-      <c r="AS19" s="19"/>
-      <c r="AT19" s="18"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="18"/>
+      <c r="M19" s="18"/>
+      <c r="N19" s="18"/>
+      <c r="O19" s="18"/>
+      <c r="P19" s="18"/>
+      <c r="Q19" s="18"/>
+      <c r="R19" s="18"/>
+      <c r="S19" s="18"/>
+      <c r="T19" s="18"/>
+      <c r="U19" s="18"/>
+      <c r="V19" s="18"/>
+      <c r="W19" s="18"/>
+      <c r="X19" s="18"/>
+      <c r="Y19" s="19"/>
+      <c r="Z19" s="20"/>
+      <c r="AA19" s="19"/>
+      <c r="AB19" s="20"/>
+      <c r="AC19" s="18"/>
+      <c r="AD19" s="18"/>
+      <c r="AE19" s="19"/>
+      <c r="AF19" s="20"/>
+      <c r="AG19" s="18"/>
+      <c r="AH19" s="18"/>
+      <c r="AI19" s="19"/>
+      <c r="AS19" s="20"/>
+      <c r="AT19" s="19"/>
     </row>
     <row r="20">
       <c r="B20" s="1"/>
@@ -1169,16 +1232,16 @@
       <c r="AT20" s="3"/>
     </row>
     <row r="21">
-      <c r="B21" s="24"/>
+      <c r="B21" s="29"/>
       <c r="C21" s="6"/>
       <c r="D21" s="7"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="24"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="29"/>
       <c r="I21" s="6"/>
       <c r="J21" s="7"/>
-      <c r="K21" s="24"/>
+      <c r="K21" s="29"/>
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
       <c r="N21" s="6"/>
@@ -1193,245 +1256,245 @@
       <c r="W21" s="6"/>
       <c r="X21" s="6"/>
       <c r="Y21" s="7"/>
-      <c r="Z21" s="24"/>
+      <c r="Z21" s="29"/>
       <c r="AA21" s="7"/>
-      <c r="AB21" s="24"/>
+      <c r="AB21" s="29"/>
       <c r="AC21" s="6"/>
       <c r="AD21" s="6"/>
       <c r="AE21" s="7"/>
-      <c r="AF21" s="24"/>
+      <c r="AF21" s="29"/>
       <c r="AG21" s="6"/>
       <c r="AH21" s="6"/>
       <c r="AI21" s="7"/>
-      <c r="AJ21" s="24"/>
+      <c r="AJ21" s="29"/>
       <c r="AK21" s="6"/>
       <c r="AL21" s="6"/>
       <c r="AM21" s="6"/>
       <c r="AN21" s="6"/>
       <c r="AO21" s="7"/>
-      <c r="AP21" s="24"/>
+      <c r="AP21" s="29"/>
       <c r="AQ21" s="6"/>
       <c r="AR21" s="7"/>
-      <c r="AS21" s="24"/>
+      <c r="AS21" s="29"/>
       <c r="AT21" s="7"/>
     </row>
     <row r="22">
-      <c r="B22" s="19"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17"/>
-      <c r="M22" s="17"/>
-      <c r="N22" s="17"/>
-      <c r="O22" s="17"/>
-      <c r="P22" s="17"/>
-      <c r="Q22" s="17"/>
-      <c r="R22" s="17"/>
-      <c r="S22" s="17"/>
-      <c r="T22" s="17"/>
-      <c r="U22" s="17"/>
-      <c r="V22" s="17"/>
-      <c r="W22" s="17"/>
-      <c r="X22" s="17"/>
-      <c r="Y22" s="17"/>
-      <c r="Z22" s="17"/>
-      <c r="AA22" s="17"/>
-      <c r="AB22" s="17"/>
-      <c r="AC22" s="17"/>
-      <c r="AD22" s="17"/>
-      <c r="AE22" s="18"/>
-      <c r="AF22" s="19"/>
-      <c r="AG22" s="25" t="inlineStr">
+      <c r="B22" s="20"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="18"/>
+      <c r="L22" s="18"/>
+      <c r="M22" s="18"/>
+      <c r="N22" s="18"/>
+      <c r="O22" s="18"/>
+      <c r="P22" s="18"/>
+      <c r="Q22" s="18"/>
+      <c r="R22" s="18"/>
+      <c r="S22" s="18"/>
+      <c r="T22" s="18"/>
+      <c r="U22" s="18"/>
+      <c r="V22" s="18"/>
+      <c r="W22" s="18"/>
+      <c r="X22" s="18"/>
+      <c r="Y22" s="18"/>
+      <c r="Z22" s="18"/>
+      <c r="AA22" s="18"/>
+      <c r="AB22" s="18"/>
+      <c r="AC22" s="18"/>
+      <c r="AD22" s="18"/>
+      <c r="AE22" s="19"/>
+      <c r="AF22" s="20"/>
+      <c r="AG22" s="35" t="inlineStr">
         <is>
           <t>（税抜金額）</t>
         </is>
       </c>
-      <c r="AH22" s="17"/>
-      <c r="AI22" s="18"/>
-      <c r="AJ22" s="19"/>
-      <c r="AK22" s="25" t="inlineStr">
+      <c r="AH22" s="18"/>
+      <c r="AI22" s="19"/>
+      <c r="AJ22" s="20"/>
+      <c r="AK22" s="35" t="inlineStr">
         <is>
           <t>(消費税)</t>
         </is>
       </c>
-      <c r="AL22" s="17"/>
-      <c r="AM22" s="18"/>
-      <c r="AN22" s="19"/>
-      <c r="AO22" s="25" t="inlineStr">
+      <c r="AL22" s="18"/>
+      <c r="AM22" s="19"/>
+      <c r="AN22" s="20"/>
+      <c r="AO22" s="35" t="inlineStr">
         <is>
           <t>(税込金額)</t>
         </is>
       </c>
-      <c r="AP22" s="17"/>
-      <c r="AQ22" s="17"/>
-      <c r="AR22" s="18"/>
-      <c r="AS22" s="19"/>
-      <c r="AT22" s="18"/>
+      <c r="AP22" s="18"/>
+      <c r="AQ22" s="18"/>
+      <c r="AR22" s="19"/>
+      <c r="AS22" s="20"/>
+      <c r="AT22" s="19"/>
     </row>
     <row r="23">
-      <c r="AA23" s="14" t="inlineStr">
+      <c r="AA23" s="10" t="inlineStr">
         <is>
           <t>非・不課税小計</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="19"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
-      <c r="L24" s="17"/>
-      <c r="M24" s="17"/>
-      <c r="N24" s="17"/>
-      <c r="O24" s="17"/>
-      <c r="P24" s="17"/>
-      <c r="Q24" s="17"/>
-      <c r="R24" s="17"/>
-      <c r="S24" s="17"/>
-      <c r="T24" s="17"/>
-      <c r="U24" s="17"/>
-      <c r="V24" s="17"/>
-      <c r="W24" s="17"/>
-      <c r="X24" s="17"/>
-      <c r="Y24" s="17"/>
-      <c r="Z24" s="17"/>
-      <c r="AA24" s="17"/>
-      <c r="AB24" s="17"/>
-      <c r="AC24" s="25" t="inlineStr">
+      <c r="B24" s="20"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="18"/>
+      <c r="K24" s="18"/>
+      <c r="L24" s="18"/>
+      <c r="M24" s="18"/>
+      <c r="N24" s="18"/>
+      <c r="O24" s="18"/>
+      <c r="P24" s="18"/>
+      <c r="Q24" s="18"/>
+      <c r="R24" s="18"/>
+      <c r="S24" s="18"/>
+      <c r="T24" s="18"/>
+      <c r="U24" s="18"/>
+      <c r="V24" s="18"/>
+      <c r="W24" s="18"/>
+      <c r="X24" s="18"/>
+      <c r="Y24" s="18"/>
+      <c r="Z24" s="18"/>
+      <c r="AA24" s="18"/>
+      <c r="AB24" s="18"/>
+      <c r="AC24" s="35" t="inlineStr">
         <is>
           <t>8%小計</t>
         </is>
       </c>
-      <c r="AD24" s="17"/>
-      <c r="AE24" s="18"/>
-      <c r="AF24" s="19"/>
-      <c r="AG24" s="17"/>
-      <c r="AH24" s="17"/>
-      <c r="AI24" s="18"/>
-      <c r="AJ24" s="19"/>
-      <c r="AK24" s="17"/>
-      <c r="AL24" s="17"/>
-      <c r="AM24" s="18"/>
-      <c r="AN24" s="19"/>
-      <c r="AO24" s="17"/>
-      <c r="AP24" s="17"/>
-      <c r="AQ24" s="17"/>
-      <c r="AR24" s="18"/>
-      <c r="AS24" s="19"/>
-      <c r="AT24" s="18"/>
+      <c r="AD24" s="18"/>
+      <c r="AE24" s="19"/>
+      <c r="AF24" s="20"/>
+      <c r="AG24" s="18"/>
+      <c r="AH24" s="18"/>
+      <c r="AI24" s="19"/>
+      <c r="AJ24" s="20"/>
+      <c r="AK24" s="18"/>
+      <c r="AL24" s="18"/>
+      <c r="AM24" s="19"/>
+      <c r="AN24" s="20"/>
+      <c r="AO24" s="18"/>
+      <c r="AP24" s="18"/>
+      <c r="AQ24" s="18"/>
+      <c r="AR24" s="19"/>
+      <c r="AS24" s="20"/>
+      <c r="AT24" s="19"/>
     </row>
     <row r="25">
-      <c r="AC25" s="14" t="inlineStr">
+      <c r="AC25" s="10" t="inlineStr">
         <is>
           <t>10%小計</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="19"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="17"/>
-      <c r="M26" s="17"/>
-      <c r="N26" s="17"/>
-      <c r="O26" s="17"/>
-      <c r="P26" s="17"/>
-      <c r="Q26" s="17"/>
-      <c r="R26" s="17"/>
-      <c r="S26" s="17"/>
-      <c r="T26" s="17"/>
-      <c r="U26" s="17"/>
-      <c r="V26" s="17"/>
-      <c r="W26" s="17"/>
-      <c r="X26" s="17"/>
-      <c r="Y26" s="17"/>
-      <c r="Z26" s="17"/>
-      <c r="AA26" s="17"/>
-      <c r="AB26" s="17"/>
-      <c r="AC26" s="17"/>
-      <c r="AD26" s="25" t="inlineStr">
+      <c r="B26" s="20"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
+      <c r="M26" s="18"/>
+      <c r="N26" s="18"/>
+      <c r="O26" s="18"/>
+      <c r="P26" s="18"/>
+      <c r="Q26" s="18"/>
+      <c r="R26" s="18"/>
+      <c r="S26" s="18"/>
+      <c r="T26" s="18"/>
+      <c r="U26" s="18"/>
+      <c r="V26" s="18"/>
+      <c r="W26" s="18"/>
+      <c r="X26" s="18"/>
+      <c r="Y26" s="18"/>
+      <c r="Z26" s="18"/>
+      <c r="AA26" s="18"/>
+      <c r="AB26" s="18"/>
+      <c r="AC26" s="18"/>
+      <c r="AD26" s="35" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="AE26" s="18"/>
-      <c r="AF26" s="19"/>
-      <c r="AG26" s="17"/>
-      <c r="AH26" s="17"/>
-      <c r="AI26" s="18"/>
-      <c r="AJ26" s="19"/>
-      <c r="AK26" s="17"/>
-      <c r="AL26" s="17"/>
-      <c r="AM26" s="18"/>
-      <c r="AN26" s="19"/>
-      <c r="AO26" s="17"/>
-      <c r="AP26" s="17"/>
-      <c r="AQ26" s="17"/>
-      <c r="AR26" s="18"/>
-      <c r="AS26" s="19"/>
-      <c r="AT26" s="18"/>
+      <c r="AE26" s="19"/>
+      <c r="AF26" s="20"/>
+      <c r="AG26" s="18"/>
+      <c r="AH26" s="18"/>
+      <c r="AI26" s="19"/>
+      <c r="AJ26" s="20"/>
+      <c r="AK26" s="18"/>
+      <c r="AL26" s="18"/>
+      <c r="AM26" s="19"/>
+      <c r="AN26" s="20"/>
+      <c r="AO26" s="18"/>
+      <c r="AP26" s="18"/>
+      <c r="AQ26" s="18"/>
+      <c r="AR26" s="19"/>
+      <c r="AS26" s="20"/>
+      <c r="AT26" s="19"/>
     </row>
     <row r="27">
-      <c r="B27" s="26" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>※提出部数</t>
         </is>
       </c>
-      <c r="E27" s="26" t="inlineStr">
+      <c r="E27" s="15" t="inlineStr">
         <is>
           <t>1部（白黒で構いません）・・・毎月５日必着</t>
         </is>
       </c>
-      <c r="AF27" s="14" t="inlineStr">
+      <c r="AF27" s="37" t="inlineStr">
         <is>
           <t>経営管理部長</t>
         </is>
       </c>
-      <c r="AI27" s="19"/>
-      <c r="AJ27" s="17"/>
-      <c r="AK27" s="17"/>
-      <c r="AL27" s="25" t="inlineStr">
+      <c r="AI27" s="20"/>
+      <c r="AJ27" s="18"/>
+      <c r="AK27" s="18"/>
+      <c r="AL27" s="38" t="inlineStr">
         <is>
           <t>検</t>
         </is>
       </c>
-      <c r="AM27" s="17"/>
-      <c r="AN27" s="17"/>
-      <c r="AO27" s="25" t="inlineStr">
+      <c r="AM27" s="18"/>
+      <c r="AN27" s="18"/>
+      <c r="AO27" s="38" t="inlineStr">
         <is>
           <t>印</t>
         </is>
       </c>
-      <c r="AP27" s="17"/>
-      <c r="AQ27" s="17"/>
-      <c r="AR27" s="18"/>
-      <c r="AS27" s="14" t="inlineStr">
+      <c r="AP27" s="18"/>
+      <c r="AQ27" s="18"/>
+      <c r="AR27" s="19"/>
+      <c r="AS27" s="39" t="inlineStr">
         <is>
           <t>入力者</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="26" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>※毎年１２月のみ２０日締切（２５日必着）翌月末日支払いとさせていただきます。</t>
         </is>
@@ -1453,20 +1516,20 @@
       <c r="AT28" s="3"/>
     </row>
     <row r="29">
-      <c r="AF29" s="24"/>
+      <c r="AF29" s="29"/>
       <c r="AG29" s="6"/>
       <c r="AH29" s="7"/>
-      <c r="AI29" s="24"/>
+      <c r="AI29" s="29"/>
       <c r="AJ29" s="7"/>
-      <c r="AK29" s="24"/>
+      <c r="AK29" s="29"/>
       <c r="AL29" s="6"/>
       <c r="AM29" s="7"/>
-      <c r="AN29" s="24"/>
+      <c r="AN29" s="29"/>
       <c r="AO29" s="7"/>
-      <c r="AP29" s="24"/>
+      <c r="AP29" s="29"/>
       <c r="AQ29" s="6"/>
       <c r="AR29" s="7"/>
-      <c r="AS29" s="24"/>
+      <c r="AS29" s="29"/>
       <c r="AT29" s="7"/>
     </row>
     <row r="32">
@@ -1567,7 +1630,7 @@
       <c r="AJ36" s="2"/>
       <c r="AK36" s="2"/>
       <c r="AL36" s="2"/>
-      <c r="AM36" s="12" t="inlineStr">
+      <c r="AM36" s="13" t="inlineStr">
         <is>
           <t>－</t>
         </is>
@@ -1581,35 +1644,35 @@
       <c r="AT36" s="3"/>
     </row>
     <row r="37">
-      <c r="AF37" s="13" t="inlineStr">
+      <c r="AF37" s="14" t="inlineStr">
         <is>
           <t>住</t>
         </is>
       </c>
-      <c r="AJ37" s="14" t="inlineStr">
+      <c r="AJ37" s="15" t="inlineStr">
         <is>
           <t>所</t>
         </is>
       </c>
-      <c r="AT37" s="15"/>
+      <c r="AT37" s="16"/>
     </row>
     <row r="38">
-      <c r="B38" s="16" t="inlineStr">
+      <c r="B38" s="17" t="inlineStr">
         <is>
           <t>支払票NO</t>
         </is>
       </c>
-      <c r="C38" s="17"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="18"/>
-      <c r="AF38" s="13" t="inlineStr">
+      <c r="C38" s="18"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="19"/>
+      <c r="AF38" s="14" t="inlineStr">
         <is>
           <t>取引先名</t>
         </is>
       </c>
-      <c r="AT38" s="15"/>
+      <c r="AT38" s="16"/>
     </row>
     <row r="39">
       <c r="B39" s="9" t="inlineStr">
@@ -1617,17 +1680,17 @@
           <t>※請求書ご提出にあたってのお願い</t>
         </is>
       </c>
-      <c r="AF39" s="13" t="inlineStr">
+      <c r="AF39" s="14" t="inlineStr">
         <is>
           <t>代表者名</t>
         </is>
       </c>
-      <c r="AS39" s="14" t="inlineStr">
+      <c r="AS39" s="21" t="inlineStr">
         <is>
           <t>印</t>
         </is>
       </c>
-      <c r="AT39" s="15"/>
+      <c r="AT39" s="16"/>
     </row>
     <row r="40">
       <c r="B40" s="9" t="inlineStr">
@@ -1650,23 +1713,23 @@
           <t>太枠内と灰色の部分</t>
         </is>
       </c>
-      <c r="AF40" s="20"/>
-      <c r="AJ40" s="14" t="inlineStr">
+      <c r="AF40" s="22"/>
+      <c r="AJ40" s="9" t="inlineStr">
         <is>
           <t>電話FAX</t>
         </is>
       </c>
-      <c r="AN40" s="14" t="inlineStr">
+      <c r="AN40" s="9" t="inlineStr">
         <is>
           <t>－－</t>
         </is>
       </c>
-      <c r="AQ40" s="14" t="inlineStr">
+      <c r="AQ40" s="9" t="inlineStr">
         <is>
           <t>－－</t>
         </is>
       </c>
-      <c r="AT40" s="15"/>
+      <c r="AT40" s="16"/>
     </row>
     <row r="41">
       <c r="E41" s="9" t="inlineStr">
@@ -1679,12 +1742,12 @@
           <t>太枠内のみ</t>
         </is>
       </c>
-      <c r="AF41" s="13" t="inlineStr">
+      <c r="AF41" s="14" t="inlineStr">
         <is>
           <t>登録番号Ｔ</t>
         </is>
       </c>
-      <c r="AT41" s="15"/>
+      <c r="AT41" s="16"/>
     </row>
     <row r="42">
       <c r="B42" s="9" t="inlineStr">
@@ -1692,7 +1755,7 @@
           <t>２．納入品目を記入しきれない場合は、総額を記入し御社の請求明細書を添付してください。</t>
         </is>
       </c>
-      <c r="AF42" s="21" t="inlineStr">
+      <c r="AF42" s="23" t="inlineStr">
         <is>
           <t>振込先情報</t>
         </is>
@@ -1702,14 +1765,14 @@
       <c r="AI42" s="6"/>
       <c r="AJ42" s="6"/>
       <c r="AK42" s="6"/>
-      <c r="AL42" s="22" t="inlineStr">
+      <c r="AL42" s="24" t="inlineStr">
         <is>
           <t>銀行預金</t>
         </is>
       </c>
       <c r="AM42" s="6"/>
       <c r="AN42" s="6"/>
-      <c r="AO42" s="22" t="inlineStr">
+      <c r="AO42" s="25" t="inlineStr">
         <is>
           <t>口座番号：支店</t>
         </is>
@@ -1721,16 +1784,16 @@
       <c r="AT42" s="7"/>
     </row>
     <row r="43">
-      <c r="B43" s="23" t="inlineStr">
+      <c r="B43" s="26" t="inlineStr">
         <is>
           <t>３．軽油税、産廃税については、「工事名（品名）」欄に個別に明記してください。</t>
         </is>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="3"/>
-      <c r="E43" s="19"/>
-      <c r="F43" s="17"/>
-      <c r="G43" s="18"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="19"/>
       <c r="H43" s="1"/>
       <c r="I43" s="2"/>
       <c r="J43" s="3"/>
@@ -1759,54 +1822,54 @@
       <c r="AG43" s="2"/>
       <c r="AH43" s="2"/>
       <c r="AI43" s="3"/>
-      <c r="AJ43" s="16" t="inlineStr">
+      <c r="AJ43" s="17" t="inlineStr">
         <is>
           <t>口座名義(ｶﾀｶﾅ)：</t>
         </is>
       </c>
-      <c r="AK43" s="17"/>
-      <c r="AL43" s="17"/>
-      <c r="AM43" s="17"/>
-      <c r="AN43" s="17"/>
-      <c r="AO43" s="17"/>
-      <c r="AP43" s="17"/>
-      <c r="AQ43" s="17"/>
-      <c r="AR43" s="18"/>
+      <c r="AK43" s="18"/>
+      <c r="AL43" s="18"/>
+      <c r="AM43" s="18"/>
+      <c r="AN43" s="18"/>
+      <c r="AO43" s="18"/>
+      <c r="AP43" s="18"/>
+      <c r="AQ43" s="18"/>
+      <c r="AR43" s="19"/>
       <c r="AS43" s="1"/>
       <c r="AT43" s="3"/>
     </row>
     <row r="44">
-      <c r="B44" s="21" t="inlineStr">
+      <c r="B44" s="27" t="inlineStr">
         <is>
           <t>工事NO</t>
         </is>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="7"/>
-      <c r="E44" s="14" t="inlineStr">
+      <c r="E44" s="28" t="inlineStr">
         <is>
           <t>科目コード</t>
         </is>
       </c>
-      <c r="F44" s="14" t="inlineStr">
+      <c r="F44" s="28" t="inlineStr">
         <is>
           <t>科目名</t>
         </is>
       </c>
-      <c r="H44" s="24"/>
-      <c r="I44" s="22" t="inlineStr">
+      <c r="H44" s="29"/>
+      <c r="I44" s="30" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
       <c r="J44" s="7"/>
-      <c r="K44" s="24"/>
+      <c r="K44" s="29"/>
       <c r="L44" s="6"/>
       <c r="M44" s="6"/>
       <c r="N44" s="6"/>
       <c r="O44" s="6"/>
       <c r="P44" s="6"/>
-      <c r="Q44" s="22" t="inlineStr">
+      <c r="Q44" s="30" t="inlineStr">
         <is>
           <t>工事名（品名）</t>
         </is>
@@ -1819,13 +1882,13 @@
       <c r="W44" s="6"/>
       <c r="X44" s="6"/>
       <c r="Y44" s="7"/>
-      <c r="Z44" s="21" t="inlineStr">
+      <c r="Z44" s="31" t="inlineStr">
         <is>
           <t>内訳NO</t>
         </is>
       </c>
       <c r="AA44" s="7"/>
-      <c r="AB44" s="21" t="inlineStr">
+      <c r="AB44" s="27" t="inlineStr">
         <is>
           <t>現在注文金額</t>
         </is>
@@ -1833,7 +1896,7 @@
       <c r="AC44" s="6"/>
       <c r="AD44" s="6"/>
       <c r="AE44" s="7"/>
-      <c r="AF44" s="21" t="inlineStr">
+      <c r="AF44" s="27" t="inlineStr">
         <is>
           <t>前回迄の支払額</t>
         </is>
@@ -1841,20 +1904,20 @@
       <c r="AG44" s="6"/>
       <c r="AH44" s="6"/>
       <c r="AI44" s="7"/>
-      <c r="AJ44" s="19"/>
-      <c r="AK44" s="17"/>
-      <c r="AL44" s="17"/>
-      <c r="AM44" s="25" t="inlineStr">
+      <c r="AJ44" s="20"/>
+      <c r="AK44" s="18"/>
+      <c r="AL44" s="18"/>
+      <c r="AM44" s="32" t="inlineStr">
         <is>
           <t>今回請求額</t>
         </is>
       </c>
-      <c r="AN44" s="17"/>
-      <c r="AO44" s="18"/>
-      <c r="AP44" s="19"/>
-      <c r="AQ44" s="17"/>
-      <c r="AR44" s="18"/>
-      <c r="AS44" s="21" t="inlineStr">
+      <c r="AN44" s="18"/>
+      <c r="AO44" s="19"/>
+      <c r="AP44" s="20"/>
+      <c r="AQ44" s="18"/>
+      <c r="AR44" s="19"/>
+      <c r="AS44" s="33" t="inlineStr">
         <is>
           <t>グリーン産業</t>
         </is>
@@ -1862,168 +1925,168 @@
       <c r="AT44" s="7"/>
     </row>
     <row r="45">
-      <c r="B45" s="19"/>
-      <c r="C45" s="17"/>
-      <c r="D45" s="18"/>
-      <c r="E45" s="19"/>
-      <c r="F45" s="17"/>
-      <c r="G45" s="18"/>
-      <c r="H45" s="19"/>
-      <c r="I45" s="17"/>
-      <c r="J45" s="18"/>
-      <c r="K45" s="19"/>
-      <c r="L45" s="17"/>
-      <c r="M45" s="17"/>
-      <c r="N45" s="17"/>
-      <c r="O45" s="17"/>
-      <c r="P45" s="17"/>
-      <c r="Q45" s="17"/>
-      <c r="R45" s="17"/>
-      <c r="S45" s="17"/>
-      <c r="T45" s="17"/>
-      <c r="U45" s="17"/>
-      <c r="V45" s="17"/>
-      <c r="W45" s="17"/>
-      <c r="X45" s="17"/>
-      <c r="Y45" s="18"/>
-      <c r="Z45" s="19"/>
-      <c r="AA45" s="18"/>
-      <c r="AB45" s="16" t="inlineStr">
+      <c r="B45" s="20"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="19"/>
+      <c r="E45" s="20"/>
+      <c r="F45" s="18"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="20"/>
+      <c r="I45" s="18"/>
+      <c r="J45" s="19"/>
+      <c r="K45" s="20"/>
+      <c r="L45" s="18"/>
+      <c r="M45" s="18"/>
+      <c r="N45" s="18"/>
+      <c r="O45" s="18"/>
+      <c r="P45" s="18"/>
+      <c r="Q45" s="18"/>
+      <c r="R45" s="18"/>
+      <c r="S45" s="18"/>
+      <c r="T45" s="18"/>
+      <c r="U45" s="18"/>
+      <c r="V45" s="18"/>
+      <c r="W45" s="18"/>
+      <c r="X45" s="18"/>
+      <c r="Y45" s="19"/>
+      <c r="Z45" s="20"/>
+      <c r="AA45" s="19"/>
+      <c r="AB45" s="34" t="inlineStr">
         <is>
           <t>（税抜金額）</t>
         </is>
       </c>
-      <c r="AC45" s="17"/>
-      <c r="AD45" s="17"/>
-      <c r="AE45" s="18"/>
-      <c r="AF45" s="19"/>
-      <c r="AG45" s="25" t="inlineStr">
+      <c r="AC45" s="18"/>
+      <c r="AD45" s="18"/>
+      <c r="AE45" s="19"/>
+      <c r="AF45" s="20"/>
+      <c r="AG45" s="35" t="inlineStr">
         <is>
           <t>（税抜金額）</t>
         </is>
       </c>
-      <c r="AH45" s="17"/>
-      <c r="AI45" s="18"/>
-      <c r="AJ45" s="14" t="inlineStr">
+      <c r="AH45" s="18"/>
+      <c r="AI45" s="19"/>
+      <c r="AJ45" s="36" t="inlineStr">
         <is>
           <t>（税抜金額）</t>
         </is>
       </c>
-      <c r="AL45" s="14" t="inlineStr">
+      <c r="AL45" s="10" t="inlineStr">
         <is>
           <t>（税抜金額）</t>
         </is>
       </c>
-      <c r="AP45" s="14" t="inlineStr">
+      <c r="AP45" s="36" t="inlineStr">
         <is>
           <t>税率</t>
         </is>
       </c>
-      <c r="AQ45" s="14" t="inlineStr">
+      <c r="AQ45" s="10" t="inlineStr">
         <is>
           <t>税率</t>
         </is>
       </c>
-      <c r="AS45" s="19"/>
-      <c r="AT45" s="18"/>
+      <c r="AS45" s="20"/>
+      <c r="AT45" s="19"/>
     </row>
     <row r="46">
-      <c r="AJ46" s="19"/>
-      <c r="AK46" s="17"/>
-      <c r="AL46" s="17"/>
-      <c r="AM46" s="17"/>
-      <c r="AN46" s="17"/>
-      <c r="AO46" s="18"/>
-      <c r="AP46" s="19"/>
-      <c r="AQ46" s="17"/>
-      <c r="AR46" s="18"/>
+      <c r="AJ46" s="20"/>
+      <c r="AK46" s="18"/>
+      <c r="AL46" s="18"/>
+      <c r="AM46" s="18"/>
+      <c r="AN46" s="18"/>
+      <c r="AO46" s="19"/>
+      <c r="AP46" s="20"/>
+      <c r="AQ46" s="18"/>
+      <c r="AR46" s="19"/>
     </row>
     <row r="47">
-      <c r="B47" s="19"/>
-      <c r="C47" s="17"/>
-      <c r="D47" s="18"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="17"/>
-      <c r="G47" s="18"/>
-      <c r="H47" s="19"/>
-      <c r="I47" s="17"/>
-      <c r="J47" s="18"/>
-      <c r="K47" s="19"/>
-      <c r="L47" s="17"/>
-      <c r="M47" s="17"/>
-      <c r="N47" s="17"/>
-      <c r="O47" s="17"/>
-      <c r="P47" s="17"/>
-      <c r="Q47" s="17"/>
-      <c r="R47" s="17"/>
-      <c r="S47" s="17"/>
-      <c r="T47" s="17"/>
-      <c r="U47" s="17"/>
-      <c r="V47" s="17"/>
-      <c r="W47" s="17"/>
-      <c r="X47" s="17"/>
-      <c r="Y47" s="18"/>
-      <c r="Z47" s="19"/>
-      <c r="AA47" s="18"/>
-      <c r="AB47" s="19"/>
-      <c r="AC47" s="17"/>
-      <c r="AD47" s="17"/>
-      <c r="AE47" s="18"/>
-      <c r="AF47" s="19"/>
-      <c r="AG47" s="17"/>
-      <c r="AH47" s="17"/>
-      <c r="AI47" s="18"/>
-      <c r="AS47" s="19"/>
-      <c r="AT47" s="18"/>
+      <c r="B47" s="20"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="18"/>
+      <c r="G47" s="19"/>
+      <c r="H47" s="20"/>
+      <c r="I47" s="18"/>
+      <c r="J47" s="19"/>
+      <c r="K47" s="20"/>
+      <c r="L47" s="18"/>
+      <c r="M47" s="18"/>
+      <c r="N47" s="18"/>
+      <c r="O47" s="18"/>
+      <c r="P47" s="18"/>
+      <c r="Q47" s="18"/>
+      <c r="R47" s="18"/>
+      <c r="S47" s="18"/>
+      <c r="T47" s="18"/>
+      <c r="U47" s="18"/>
+      <c r="V47" s="18"/>
+      <c r="W47" s="18"/>
+      <c r="X47" s="18"/>
+      <c r="Y47" s="19"/>
+      <c r="Z47" s="20"/>
+      <c r="AA47" s="19"/>
+      <c r="AB47" s="20"/>
+      <c r="AC47" s="18"/>
+      <c r="AD47" s="18"/>
+      <c r="AE47" s="19"/>
+      <c r="AF47" s="20"/>
+      <c r="AG47" s="18"/>
+      <c r="AH47" s="18"/>
+      <c r="AI47" s="19"/>
+      <c r="AS47" s="20"/>
+      <c r="AT47" s="19"/>
     </row>
     <row r="48">
-      <c r="AJ48" s="19"/>
-      <c r="AK48" s="17"/>
-      <c r="AL48" s="17"/>
-      <c r="AM48" s="17"/>
-      <c r="AN48" s="17"/>
-      <c r="AO48" s="18"/>
-      <c r="AP48" s="19"/>
-      <c r="AQ48" s="17"/>
-      <c r="AR48" s="18"/>
+      <c r="AJ48" s="20"/>
+      <c r="AK48" s="18"/>
+      <c r="AL48" s="18"/>
+      <c r="AM48" s="18"/>
+      <c r="AN48" s="18"/>
+      <c r="AO48" s="19"/>
+      <c r="AP48" s="20"/>
+      <c r="AQ48" s="18"/>
+      <c r="AR48" s="19"/>
     </row>
     <row r="49">
-      <c r="B49" s="19"/>
-      <c r="C49" s="17"/>
-      <c r="D49" s="18"/>
-      <c r="E49" s="19"/>
-      <c r="F49" s="17"/>
-      <c r="G49" s="18"/>
-      <c r="H49" s="19"/>
-      <c r="I49" s="17"/>
-      <c r="J49" s="18"/>
-      <c r="K49" s="19"/>
-      <c r="L49" s="17"/>
-      <c r="M49" s="17"/>
-      <c r="N49" s="17"/>
-      <c r="O49" s="17"/>
-      <c r="P49" s="17"/>
-      <c r="Q49" s="17"/>
-      <c r="R49" s="17"/>
-      <c r="S49" s="17"/>
-      <c r="T49" s="17"/>
-      <c r="U49" s="17"/>
-      <c r="V49" s="17"/>
-      <c r="W49" s="17"/>
-      <c r="X49" s="17"/>
-      <c r="Y49" s="18"/>
-      <c r="Z49" s="19"/>
-      <c r="AA49" s="18"/>
-      <c r="AB49" s="19"/>
-      <c r="AC49" s="17"/>
-      <c r="AD49" s="17"/>
-      <c r="AE49" s="18"/>
-      <c r="AF49" s="19"/>
-      <c r="AG49" s="17"/>
-      <c r="AH49" s="17"/>
-      <c r="AI49" s="18"/>
-      <c r="AS49" s="19"/>
-      <c r="AT49" s="18"/>
+      <c r="B49" s="20"/>
+      <c r="C49" s="18"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="20"/>
+      <c r="F49" s="18"/>
+      <c r="G49" s="19"/>
+      <c r="H49" s="20"/>
+      <c r="I49" s="18"/>
+      <c r="J49" s="19"/>
+      <c r="K49" s="20"/>
+      <c r="L49" s="18"/>
+      <c r="M49" s="18"/>
+      <c r="N49" s="18"/>
+      <c r="O49" s="18"/>
+      <c r="P49" s="18"/>
+      <c r="Q49" s="18"/>
+      <c r="R49" s="18"/>
+      <c r="S49" s="18"/>
+      <c r="T49" s="18"/>
+      <c r="U49" s="18"/>
+      <c r="V49" s="18"/>
+      <c r="W49" s="18"/>
+      <c r="X49" s="18"/>
+      <c r="Y49" s="19"/>
+      <c r="Z49" s="20"/>
+      <c r="AA49" s="19"/>
+      <c r="AB49" s="20"/>
+      <c r="AC49" s="18"/>
+      <c r="AD49" s="18"/>
+      <c r="AE49" s="19"/>
+      <c r="AF49" s="20"/>
+      <c r="AG49" s="18"/>
+      <c r="AH49" s="18"/>
+      <c r="AI49" s="19"/>
+      <c r="AS49" s="20"/>
+      <c r="AT49" s="19"/>
     </row>
     <row r="50">
       <c r="B50" s="1"/>
@@ -2070,16 +2133,16 @@
       <c r="AT50" s="3"/>
     </row>
     <row r="51">
-      <c r="B51" s="24"/>
+      <c r="B51" s="29"/>
       <c r="C51" s="6"/>
       <c r="D51" s="7"/>
-      <c r="E51" s="19"/>
-      <c r="F51" s="17"/>
-      <c r="G51" s="18"/>
-      <c r="H51" s="24"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="18"/>
+      <c r="G51" s="19"/>
+      <c r="H51" s="29"/>
       <c r="I51" s="6"/>
       <c r="J51" s="7"/>
-      <c r="K51" s="24"/>
+      <c r="K51" s="29"/>
       <c r="L51" s="6"/>
       <c r="M51" s="6"/>
       <c r="N51" s="6"/>
@@ -2094,217 +2157,217 @@
       <c r="W51" s="6"/>
       <c r="X51" s="6"/>
       <c r="Y51" s="7"/>
-      <c r="Z51" s="24"/>
+      <c r="Z51" s="29"/>
       <c r="AA51" s="7"/>
-      <c r="AB51" s="24"/>
+      <c r="AB51" s="29"/>
       <c r="AC51" s="6"/>
       <c r="AD51" s="6"/>
       <c r="AE51" s="7"/>
-      <c r="AF51" s="24"/>
+      <c r="AF51" s="29"/>
       <c r="AG51" s="6"/>
       <c r="AH51" s="6"/>
       <c r="AI51" s="7"/>
-      <c r="AJ51" s="24"/>
+      <c r="AJ51" s="29"/>
       <c r="AK51" s="6"/>
       <c r="AL51" s="6"/>
       <c r="AM51" s="6"/>
       <c r="AN51" s="6"/>
       <c r="AO51" s="7"/>
-      <c r="AP51" s="24"/>
+      <c r="AP51" s="29"/>
       <c r="AQ51" s="6"/>
       <c r="AR51" s="7"/>
-      <c r="AS51" s="24"/>
+      <c r="AS51" s="29"/>
       <c r="AT51" s="7"/>
     </row>
     <row r="52">
-      <c r="B52" s="19"/>
-      <c r="C52" s="17"/>
-      <c r="D52" s="17"/>
-      <c r="E52" s="17"/>
-      <c r="F52" s="17"/>
-      <c r="G52" s="17"/>
-      <c r="H52" s="17"/>
-      <c r="I52" s="17"/>
-      <c r="J52" s="17"/>
-      <c r="K52" s="17"/>
-      <c r="L52" s="17"/>
-      <c r="M52" s="17"/>
-      <c r="N52" s="17"/>
-      <c r="O52" s="17"/>
-      <c r="P52" s="17"/>
-      <c r="Q52" s="17"/>
-      <c r="R52" s="17"/>
-      <c r="S52" s="17"/>
-      <c r="T52" s="17"/>
-      <c r="U52" s="17"/>
-      <c r="V52" s="17"/>
-      <c r="W52" s="17"/>
-      <c r="X52" s="17"/>
-      <c r="Y52" s="17"/>
-      <c r="Z52" s="17"/>
-      <c r="AA52" s="17"/>
-      <c r="AB52" s="17"/>
-      <c r="AC52" s="17"/>
-      <c r="AD52" s="17"/>
-      <c r="AE52" s="18"/>
-      <c r="AF52" s="19"/>
-      <c r="AG52" s="25" t="inlineStr">
+      <c r="B52" s="20"/>
+      <c r="C52" s="18"/>
+      <c r="D52" s="18"/>
+      <c r="E52" s="18"/>
+      <c r="F52" s="18"/>
+      <c r="G52" s="18"/>
+      <c r="H52" s="18"/>
+      <c r="I52" s="18"/>
+      <c r="J52" s="18"/>
+      <c r="K52" s="18"/>
+      <c r="L52" s="18"/>
+      <c r="M52" s="18"/>
+      <c r="N52" s="18"/>
+      <c r="O52" s="18"/>
+      <c r="P52" s="18"/>
+      <c r="Q52" s="18"/>
+      <c r="R52" s="18"/>
+      <c r="S52" s="18"/>
+      <c r="T52" s="18"/>
+      <c r="U52" s="18"/>
+      <c r="V52" s="18"/>
+      <c r="W52" s="18"/>
+      <c r="X52" s="18"/>
+      <c r="Y52" s="18"/>
+      <c r="Z52" s="18"/>
+      <c r="AA52" s="18"/>
+      <c r="AB52" s="18"/>
+      <c r="AC52" s="18"/>
+      <c r="AD52" s="18"/>
+      <c r="AE52" s="19"/>
+      <c r="AF52" s="20"/>
+      <c r="AG52" s="35" t="inlineStr">
         <is>
           <t>（税抜金額）</t>
         </is>
       </c>
-      <c r="AH52" s="17"/>
-      <c r="AI52" s="18"/>
-      <c r="AJ52" s="19"/>
-      <c r="AK52" s="25" t="inlineStr">
+      <c r="AH52" s="18"/>
+      <c r="AI52" s="19"/>
+      <c r="AJ52" s="20"/>
+      <c r="AK52" s="35" t="inlineStr">
         <is>
           <t>(消費税)</t>
         </is>
       </c>
-      <c r="AL52" s="17"/>
-      <c r="AM52" s="18"/>
-      <c r="AN52" s="19"/>
-      <c r="AO52" s="25" t="inlineStr">
+      <c r="AL52" s="18"/>
+      <c r="AM52" s="19"/>
+      <c r="AN52" s="20"/>
+      <c r="AO52" s="35" t="inlineStr">
         <is>
           <t>(税込金額)</t>
         </is>
       </c>
-      <c r="AP52" s="17"/>
-      <c r="AQ52" s="17"/>
-      <c r="AR52" s="18"/>
-      <c r="AS52" s="19"/>
-      <c r="AT52" s="18"/>
+      <c r="AP52" s="18"/>
+      <c r="AQ52" s="18"/>
+      <c r="AR52" s="19"/>
+      <c r="AS52" s="20"/>
+      <c r="AT52" s="19"/>
     </row>
     <row r="53">
-      <c r="AA53" s="14" t="inlineStr">
+      <c r="AA53" s="10" t="inlineStr">
         <is>
           <t>非・不課税小計</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="19"/>
-      <c r="C54" s="17"/>
-      <c r="D54" s="17"/>
-      <c r="E54" s="17"/>
-      <c r="F54" s="17"/>
-      <c r="G54" s="17"/>
-      <c r="H54" s="17"/>
-      <c r="I54" s="17"/>
-      <c r="J54" s="17"/>
-      <c r="K54" s="17"/>
-      <c r="L54" s="17"/>
-      <c r="M54" s="17"/>
-      <c r="N54" s="17"/>
-      <c r="O54" s="17"/>
-      <c r="P54" s="17"/>
-      <c r="Q54" s="17"/>
-      <c r="R54" s="17"/>
-      <c r="S54" s="17"/>
-      <c r="T54" s="17"/>
-      <c r="U54" s="17"/>
-      <c r="V54" s="17"/>
-      <c r="W54" s="17"/>
-      <c r="X54" s="17"/>
-      <c r="Y54" s="17"/>
-      <c r="Z54" s="17"/>
-      <c r="AA54" s="17"/>
-      <c r="AB54" s="17"/>
-      <c r="AC54" s="25" t="inlineStr">
+      <c r="B54" s="20"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="18"/>
+      <c r="E54" s="18"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="18"/>
+      <c r="H54" s="18"/>
+      <c r="I54" s="18"/>
+      <c r="J54" s="18"/>
+      <c r="K54" s="18"/>
+      <c r="L54" s="18"/>
+      <c r="M54" s="18"/>
+      <c r="N54" s="18"/>
+      <c r="O54" s="18"/>
+      <c r="P54" s="18"/>
+      <c r="Q54" s="18"/>
+      <c r="R54" s="18"/>
+      <c r="S54" s="18"/>
+      <c r="T54" s="18"/>
+      <c r="U54" s="18"/>
+      <c r="V54" s="18"/>
+      <c r="W54" s="18"/>
+      <c r="X54" s="18"/>
+      <c r="Y54" s="18"/>
+      <c r="Z54" s="18"/>
+      <c r="AA54" s="18"/>
+      <c r="AB54" s="18"/>
+      <c r="AC54" s="35" t="inlineStr">
         <is>
           <t>8%小計</t>
         </is>
       </c>
-      <c r="AD54" s="17"/>
-      <c r="AE54" s="18"/>
-      <c r="AF54" s="19"/>
-      <c r="AG54" s="17"/>
-      <c r="AH54" s="17"/>
-      <c r="AI54" s="18"/>
-      <c r="AJ54" s="19"/>
-      <c r="AK54" s="17"/>
-      <c r="AL54" s="17"/>
-      <c r="AM54" s="18"/>
-      <c r="AN54" s="19"/>
-      <c r="AO54" s="17"/>
-      <c r="AP54" s="17"/>
-      <c r="AQ54" s="17"/>
-      <c r="AR54" s="18"/>
-      <c r="AS54" s="19"/>
-      <c r="AT54" s="18"/>
+      <c r="AD54" s="18"/>
+      <c r="AE54" s="19"/>
+      <c r="AF54" s="20"/>
+      <c r="AG54" s="18"/>
+      <c r="AH54" s="18"/>
+      <c r="AI54" s="19"/>
+      <c r="AJ54" s="20"/>
+      <c r="AK54" s="18"/>
+      <c r="AL54" s="18"/>
+      <c r="AM54" s="19"/>
+      <c r="AN54" s="20"/>
+      <c r="AO54" s="18"/>
+      <c r="AP54" s="18"/>
+      <c r="AQ54" s="18"/>
+      <c r="AR54" s="19"/>
+      <c r="AS54" s="20"/>
+      <c r="AT54" s="19"/>
     </row>
     <row r="55">
-      <c r="AC55" s="14" t="inlineStr">
+      <c r="AC55" s="10" t="inlineStr">
         <is>
           <t>10%小計</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="19"/>
-      <c r="C56" s="17"/>
-      <c r="D56" s="17"/>
-      <c r="E56" s="17"/>
-      <c r="F56" s="17"/>
-      <c r="G56" s="17"/>
-      <c r="H56" s="17"/>
-      <c r="I56" s="17"/>
-      <c r="J56" s="17"/>
-      <c r="K56" s="17"/>
-      <c r="L56" s="17"/>
-      <c r="M56" s="17"/>
-      <c r="N56" s="17"/>
-      <c r="O56" s="17"/>
-      <c r="P56" s="17"/>
-      <c r="Q56" s="17"/>
-      <c r="R56" s="17"/>
-      <c r="S56" s="17"/>
-      <c r="T56" s="17"/>
-      <c r="U56" s="17"/>
-      <c r="V56" s="17"/>
-      <c r="W56" s="17"/>
-      <c r="X56" s="17"/>
-      <c r="Y56" s="17"/>
-      <c r="Z56" s="17"/>
-      <c r="AA56" s="17"/>
-      <c r="AB56" s="17"/>
-      <c r="AC56" s="17"/>
-      <c r="AD56" s="25" t="inlineStr">
+      <c r="B56" s="20"/>
+      <c r="C56" s="18"/>
+      <c r="D56" s="18"/>
+      <c r="E56" s="18"/>
+      <c r="F56" s="18"/>
+      <c r="G56" s="18"/>
+      <c r="H56" s="18"/>
+      <c r="I56" s="18"/>
+      <c r="J56" s="18"/>
+      <c r="K56" s="18"/>
+      <c r="L56" s="18"/>
+      <c r="M56" s="18"/>
+      <c r="N56" s="18"/>
+      <c r="O56" s="18"/>
+      <c r="P56" s="18"/>
+      <c r="Q56" s="18"/>
+      <c r="R56" s="18"/>
+      <c r="S56" s="18"/>
+      <c r="T56" s="18"/>
+      <c r="U56" s="18"/>
+      <c r="V56" s="18"/>
+      <c r="W56" s="18"/>
+      <c r="X56" s="18"/>
+      <c r="Y56" s="18"/>
+      <c r="Z56" s="18"/>
+      <c r="AA56" s="18"/>
+      <c r="AB56" s="18"/>
+      <c r="AC56" s="18"/>
+      <c r="AD56" s="35" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="AE56" s="18"/>
-      <c r="AF56" s="19"/>
-      <c r="AG56" s="17"/>
-      <c r="AH56" s="17"/>
-      <c r="AI56" s="18"/>
-      <c r="AJ56" s="19"/>
-      <c r="AK56" s="17"/>
-      <c r="AL56" s="17"/>
-      <c r="AM56" s="18"/>
-      <c r="AN56" s="19"/>
-      <c r="AO56" s="17"/>
-      <c r="AP56" s="17"/>
-      <c r="AQ56" s="17"/>
-      <c r="AR56" s="18"/>
-      <c r="AS56" s="19"/>
-      <c r="AT56" s="18"/>
+      <c r="AE56" s="19"/>
+      <c r="AF56" s="20"/>
+      <c r="AG56" s="18"/>
+      <c r="AH56" s="18"/>
+      <c r="AI56" s="19"/>
+      <c r="AJ56" s="20"/>
+      <c r="AK56" s="18"/>
+      <c r="AL56" s="18"/>
+      <c r="AM56" s="19"/>
+      <c r="AN56" s="20"/>
+      <c r="AO56" s="18"/>
+      <c r="AP56" s="18"/>
+      <c r="AQ56" s="18"/>
+      <c r="AR56" s="19"/>
+      <c r="AS56" s="20"/>
+      <c r="AT56" s="19"/>
     </row>
     <row r="57">
-      <c r="B57" s="26" t="inlineStr">
+      <c r="B57" s="15" t="inlineStr">
         <is>
           <t>※提出部数</t>
         </is>
       </c>
-      <c r="E57" s="26" t="inlineStr">
+      <c r="E57" s="15" t="inlineStr">
         <is>
           <t>1部（白黒で構いません）・・・毎月５日必着</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="26" t="inlineStr">
+      <c r="B58" s="15" t="inlineStr">
         <is>
           <t>※毎年１２月のみ２０日締切（２５日必着）翌月末日支払いとさせていただきます。</t>
         </is>

--- a/data/out/test0/seikyuusyo202505_Python版_2pt.xlsx
+++ b/data/out/test0/seikyuusyo202505_Python版_2pt.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Sheet'!$A$1:$BG$62</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Sheet'!$A$1:$BH$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -93,7 +93,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -167,23 +167,36 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -191,12 +204,14 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -213,14 +228,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -235,9 +252,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -250,13 +264,28 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -269,12 +298,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -642,7 +665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:BF62"/>
+  <dimension ref="B2:BG62"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.625" defaultRowHeight="18.25" customHeight="1"/>
   <sheetData>
     <row r="2">
@@ -659,83 +682,95 @@
       <c r="BD2" s="2"/>
       <c r="BE2" s="2"/>
       <c r="BF2" s="3"/>
+      <c r="BG2" s="4"/>
     </row>
     <row r="3">
-      <c r="AA3" s="4" t="inlineStr">
+      <c r="AA3" s="5" t="inlineStr">
         <is>
           <t>請</t>
         </is>
       </c>
-      <c r="AD3" s="4" t="inlineStr">
+      <c r="AD3" s="5" t="inlineStr">
         <is>
           <t>求</t>
         </is>
       </c>
-      <c r="AG3" s="4" t="inlineStr">
+      <c r="AG3" s="5" t="inlineStr">
         <is>
           <t>書</t>
         </is>
       </c>
-      <c r="AX3" s="5"/>
-      <c r="AY3" s="6"/>
-      <c r="AZ3" s="6"/>
-      <c r="BA3" s="6"/>
-      <c r="BB3" s="6"/>
-      <c r="BC3" s="6"/>
-      <c r="BD3" s="6"/>
-      <c r="BE3" s="6"/>
-      <c r="BF3" s="7"/>
+      <c r="AX3" s="6"/>
+      <c r="AY3" s="7"/>
+      <c r="AZ3" s="7"/>
+      <c r="BA3" s="7"/>
+      <c r="BB3" s="7"/>
+      <c r="BC3" s="7"/>
+      <c r="BD3" s="7"/>
+      <c r="BE3" s="7"/>
+      <c r="BF3" s="8"/>
+      <c r="BG3" s="4"/>
     </row>
     <row r="4">
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>グリーン産業株式会社</t>
         </is>
       </c>
-      <c r="K4" s="8" t="inlineStr">
+      <c r="K4" s="9" t="inlineStr">
         <is>
           <t>御中</t>
         </is>
       </c>
-      <c r="AO4" s="9" t="inlineStr">
+      <c r="AO4" s="10" t="inlineStr">
         <is>
           <t>取引先コード</t>
         </is>
       </c>
-      <c r="AS4" s="10"/>
-      <c r="AT4" s="2"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
       <c r="AX4" s="2"/>
       <c r="AY4" s="2"/>
       <c r="AZ4" s="2"/>
-      <c r="BA4" s="3"/>
+      <c r="BA4" s="12"/>
     </row>
     <row r="5">
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>下記のとおり請求致します。</t>
         </is>
       </c>
-      <c r="AS5" s="5"/>
-      <c r="AT5" s="12" t="inlineStr">
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="2"/>
+      <c r="AP5" s="2"/>
+      <c r="AQ5" s="2"/>
+      <c r="AR5" s="2"/>
+      <c r="AS5" s="6"/>
+      <c r="AT5" s="14" t="inlineStr">
         <is>
           <t>（必ずご記入ください）</t>
         </is>
       </c>
-      <c r="AU5" s="6"/>
-      <c r="AV5" s="6"/>
-      <c r="AW5" s="6"/>
-      <c r="AX5" s="6"/>
-      <c r="AY5" s="6"/>
-      <c r="AZ5" s="6"/>
-      <c r="BA5" s="7"/>
+      <c r="AU5" s="7"/>
+      <c r="AV5" s="7"/>
+      <c r="AW5" s="7"/>
+      <c r="AX5" s="7"/>
+      <c r="AY5" s="7"/>
+      <c r="AZ5" s="7"/>
+      <c r="BA5" s="15"/>
+      <c r="BB5" s="2"/>
+      <c r="BC5" s="2"/>
+      <c r="BD5" s="2"/>
+      <c r="BE5" s="2"/>
+      <c r="BF5" s="11"/>
     </row>
     <row r="6">
-      <c r="AN6" s="10"/>
+      <c r="AN6" s="11"/>
       <c r="AO6" s="2"/>
-      <c r="AP6" s="13" t="inlineStr">
+      <c r="AP6" s="16" t="inlineStr">
         <is>
           <t>〒</t>
         </is>
@@ -746,7 +781,7 @@
       <c r="AT6" s="2"/>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
-      <c r="AW6" s="14" t="inlineStr">
+      <c r="AW6" s="17" t="inlineStr">
         <is>
           <t>－</t>
         </is>
@@ -759,280 +794,357 @@
       <c r="BC6" s="2"/>
       <c r="BD6" s="2"/>
       <c r="BE6" s="3"/>
+      <c r="BF6" s="11"/>
     </row>
     <row r="7">
-      <c r="AN7" s="15" t="inlineStr">
+      <c r="AN7" s="18" t="inlineStr">
         <is>
           <t>住</t>
         </is>
       </c>
-      <c r="AS7" s="16" t="inlineStr">
+      <c r="AS7" s="19" t="inlineStr">
         <is>
           <t>所</t>
         </is>
       </c>
-      <c r="BE7" s="17"/>
+      <c r="BE7" s="20"/>
+      <c r="BF7" s="4"/>
     </row>
     <row r="8">
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>支払票NO</t>
         </is>
       </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="20"/>
-      <c r="AN8" s="15" t="inlineStr">
+      <c r="C8" s="7"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="11"/>
+      <c r="AN8" s="18" t="inlineStr">
         <is>
           <t>取引先名</t>
         </is>
       </c>
-      <c r="BE8" s="17"/>
+      <c r="BE8" s="20"/>
+      <c r="BF8" s="4"/>
     </row>
     <row r="9">
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>※請求書ご提出にあたってのお願い</t>
         </is>
       </c>
-      <c r="AN9" s="15" t="inlineStr">
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="11"/>
+      <c r="AN9" s="18" t="inlineStr">
         <is>
           <t>代表者名</t>
         </is>
       </c>
-      <c r="BE9" s="22" t="inlineStr">
+      <c r="BE9" s="23" t="inlineStr">
         <is>
           <t>印</t>
         </is>
       </c>
+      <c r="BF9" s="4"/>
     </row>
     <row r="10">
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>１．記入項目について</t>
         </is>
       </c>
-      <c r="AN10" s="23"/>
-      <c r="AT10" s="11" t="inlineStr">
+      <c r="E10" s="11"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
+      <c r="Y10" s="2"/>
+      <c r="Z10" s="2"/>
+      <c r="AA10" s="2"/>
+      <c r="AB10" s="2"/>
+      <c r="AC10" s="2"/>
+      <c r="AD10" s="2"/>
+      <c r="AE10" s="2"/>
+      <c r="AF10" s="11"/>
+      <c r="AN10" s="4"/>
+      <c r="AT10" s="13" t="inlineStr">
         <is>
           <t>電話FAX</t>
         </is>
       </c>
-      <c r="AX10" s="11" t="inlineStr">
+      <c r="AX10" s="13" t="inlineStr">
         <is>
           <t>－</t>
         </is>
       </c>
-      <c r="BB10" s="11" t="inlineStr">
+      <c r="BB10" s="13" t="inlineStr">
         <is>
           <t>－</t>
         </is>
       </c>
-      <c r="BE10" s="17"/>
+      <c r="BE10" s="20"/>
+      <c r="BF10" s="4"/>
     </row>
     <row r="11">
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t>注文書が発行されている場合</t>
         </is>
       </c>
-      <c r="O11" s="11" t="inlineStr">
+      <c r="O11" s="13" t="inlineStr">
         <is>
           <t>・・・</t>
         </is>
       </c>
-      <c r="R11" s="11" t="inlineStr">
+      <c r="R11" s="13" t="inlineStr">
         <is>
           <t>太枠内と灰色の部分</t>
         </is>
       </c>
-      <c r="AN11" s="23"/>
-      <c r="AX11" s="11" t="inlineStr">
+      <c r="AF11" s="4"/>
+      <c r="AN11" s="4"/>
+      <c r="AX11" s="13" t="inlineStr">
         <is>
           <t>－</t>
         </is>
       </c>
-      <c r="BB11" s="11" t="inlineStr">
+      <c r="BB11" s="13" t="inlineStr">
         <is>
           <t>－</t>
         </is>
       </c>
-      <c r="BE11" s="17"/>
+      <c r="BE11" s="20"/>
+      <c r="BF11" s="4"/>
     </row>
     <row r="12">
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>２．納入品目を記入しきれない場合は、総額を記入し御社の請求明細書を添付してください。</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>注文書が発行されていない場合・・・</t>
         </is>
       </c>
-      <c r="R12" s="11" t="inlineStr">
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="17" t="inlineStr">
         <is>
           <t>太枠内のみ</t>
         </is>
       </c>
-      <c r="AN12" s="15" t="inlineStr">
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="2"/>
+      <c r="W12" s="2"/>
+      <c r="X12" s="2"/>
+      <c r="Y12" s="2"/>
+      <c r="Z12" s="2"/>
+      <c r="AA12" s="2"/>
+      <c r="AB12" s="2"/>
+      <c r="AC12" s="2"/>
+      <c r="AD12" s="2"/>
+      <c r="AE12" s="2"/>
+      <c r="AF12" s="11"/>
+      <c r="AN12" s="18" t="inlineStr">
         <is>
           <t>登録番号Ｔ</t>
         </is>
       </c>
-      <c r="AV12" s="16" t="inlineStr">
+      <c r="AV12" s="19" t="inlineStr">
         <is>
           <t>銀行預金</t>
         </is>
       </c>
-      <c r="AZ12" s="11" t="inlineStr">
+      <c r="AZ12" s="13" t="inlineStr">
         <is>
           <t>口座番号：支店</t>
         </is>
       </c>
-      <c r="BE12" s="17"/>
+      <c r="BE12" s="20"/>
+      <c r="BF12" s="4"/>
     </row>
     <row r="13">
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>３．軽油税、産廃税については、「工事名（品名）」欄に個別に明記してください。</t>
         </is>
       </c>
-      <c r="AN13" s="5"/>
-      <c r="AO13" s="6"/>
-      <c r="AP13" s="6"/>
-      <c r="AQ13" s="6"/>
-      <c r="AR13" s="6"/>
-      <c r="AS13" s="6"/>
-      <c r="AT13" s="24" t="inlineStr">
+      <c r="AN13" s="6"/>
+      <c r="AO13" s="7"/>
+      <c r="AP13" s="7"/>
+      <c r="AQ13" s="7"/>
+      <c r="AR13" s="7"/>
+      <c r="AS13" s="7"/>
+      <c r="AT13" s="25" t="inlineStr">
         <is>
           <t>口座名義(ｶﾀｶﾅ)：</t>
         </is>
       </c>
-      <c r="AU13" s="6"/>
-      <c r="AV13" s="6"/>
-      <c r="AW13" s="6"/>
-      <c r="AX13" s="6"/>
-      <c r="AY13" s="6"/>
-      <c r="AZ13" s="6"/>
-      <c r="BA13" s="6"/>
-      <c r="BB13" s="6"/>
-      <c r="BC13" s="6"/>
-      <c r="BD13" s="6"/>
-      <c r="BE13" s="7"/>
+      <c r="AU13" s="7"/>
+      <c r="AV13" s="7"/>
+      <c r="AW13" s="7"/>
+      <c r="AX13" s="7"/>
+      <c r="AY13" s="7"/>
+      <c r="AZ13" s="7"/>
+      <c r="BA13" s="7"/>
+      <c r="BB13" s="7"/>
+      <c r="BC13" s="7"/>
+      <c r="BD13" s="7"/>
+      <c r="BE13" s="8"/>
+      <c r="BF13" s="11"/>
     </row>
     <row r="14">
-      <c r="B14" s="25" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>工事NO</t>
         </is>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="26" t="inlineStr">
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="27" t="inlineStr">
         <is>
           <t>科目コード</t>
         </is>
       </c>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="26" t="inlineStr">
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="27" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="L14" s="20"/>
-      <c r="M14" s="21"/>
-      <c r="N14" s="19"/>
-      <c r="O14" s="19"/>
-      <c r="P14" s="19"/>
-      <c r="Q14" s="19"/>
-      <c r="R14" s="19"/>
-      <c r="S14" s="19"/>
-      <c r="T14" s="19"/>
-      <c r="U14" s="26" t="inlineStr">
+      <c r="L14" s="8"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="27" t="inlineStr">
         <is>
           <t>工事名（品名）</t>
         </is>
       </c>
-      <c r="V14" s="19"/>
-      <c r="W14" s="19"/>
-      <c r="X14" s="19"/>
-      <c r="Y14" s="19"/>
-      <c r="Z14" s="19"/>
-      <c r="AA14" s="19"/>
-      <c r="AB14" s="19"/>
-      <c r="AC14" s="19"/>
-      <c r="AD14" s="19"/>
-      <c r="AE14" s="20"/>
-      <c r="AF14" s="21"/>
-      <c r="AG14" s="27" t="inlineStr">
+      <c r="V14" s="7"/>
+      <c r="W14" s="7"/>
+      <c r="X14" s="7"/>
+      <c r="Y14" s="7"/>
+      <c r="Z14" s="7"/>
+      <c r="AA14" s="7"/>
+      <c r="AB14" s="7"/>
+      <c r="AC14" s="7"/>
+      <c r="AD14" s="7"/>
+      <c r="AE14" s="8"/>
+      <c r="AF14" s="6"/>
+      <c r="AG14" s="28" t="inlineStr">
         <is>
           <t>内訳NO</t>
         </is>
       </c>
-      <c r="AH14" s="20"/>
-      <c r="AI14" s="25" t="inlineStr">
+      <c r="AH14" s="8"/>
+      <c r="AI14" s="26" t="inlineStr">
         <is>
           <t>現在注文金額</t>
         </is>
       </c>
-      <c r="AJ14" s="19"/>
-      <c r="AK14" s="19"/>
-      <c r="AL14" s="19"/>
-      <c r="AM14" s="20"/>
-      <c r="AN14" s="25" t="inlineStr">
+      <c r="AJ14" s="7"/>
+      <c r="AK14" s="7"/>
+      <c r="AL14" s="7"/>
+      <c r="AM14" s="8"/>
+      <c r="AN14" s="26" t="inlineStr">
         <is>
           <t>前回迄の支払額</t>
         </is>
       </c>
-      <c r="AO14" s="19"/>
-      <c r="AP14" s="19"/>
-      <c r="AQ14" s="19"/>
-      <c r="AR14" s="20"/>
-      <c r="AS14" s="21"/>
-      <c r="AT14" s="19"/>
-      <c r="AU14" s="19"/>
-      <c r="AV14" s="19"/>
-      <c r="AW14" s="26" t="inlineStr">
+      <c r="AO14" s="7"/>
+      <c r="AP14" s="7"/>
+      <c r="AQ14" s="7"/>
+      <c r="AR14" s="8"/>
+      <c r="AS14" s="6"/>
+      <c r="AT14" s="6"/>
+      <c r="AU14" s="7"/>
+      <c r="AV14" s="7"/>
+      <c r="AW14" s="27" t="inlineStr">
         <is>
           <t>今回請求額</t>
         </is>
       </c>
-      <c r="AX14" s="19"/>
-      <c r="AY14" s="19"/>
-      <c r="AZ14" s="19"/>
-      <c r="BA14" s="19"/>
-      <c r="BB14" s="19"/>
-      <c r="BC14" s="20"/>
-      <c r="BD14" s="28" t="inlineStr">
+      <c r="AX14" s="7"/>
+      <c r="AY14" s="7"/>
+      <c r="AZ14" s="7"/>
+      <c r="BA14" s="7"/>
+      <c r="BB14" s="7"/>
+      <c r="BC14" s="8"/>
+      <c r="BD14" s="29" t="inlineStr">
         <is>
           <t>グリーン産業</t>
         </is>
       </c>
-      <c r="BE14" s="19"/>
-      <c r="BF14" s="20"/>
+      <c r="BE14" s="7"/>
+      <c r="BF14" s="15"/>
+      <c r="BG14" s="4"/>
     </row>
     <row r="15">
-      <c r="B15" s="10"/>
+      <c r="B15" s="11"/>
       <c r="C15" s="2"/>
       <c r="D15" s="3"/>
-      <c r="F15" s="29" t="inlineStr">
+      <c r="E15" s="6"/>
+      <c r="F15" s="27" t="inlineStr">
         <is>
           <t>科目名</t>
         </is>
       </c>
-      <c r="J15" s="10"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="11"/>
       <c r="K15" s="2"/>
       <c r="L15" s="3"/>
-      <c r="M15" s="10"/>
+      <c r="M15" s="11"/>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
@@ -1051,7 +1163,7 @@
       <c r="AC15" s="2"/>
       <c r="AD15" s="2"/>
       <c r="AE15" s="3"/>
-      <c r="AF15" s="10"/>
+      <c r="AF15" s="11"/>
       <c r="AG15" s="2"/>
       <c r="AH15" s="3"/>
       <c r="AI15" s="30" t="inlineStr">
@@ -1063,7 +1175,7 @@
       <c r="AK15" s="2"/>
       <c r="AL15" s="2"/>
       <c r="AM15" s="3"/>
-      <c r="AN15" s="10"/>
+      <c r="AN15" s="11"/>
       <c r="AO15" s="31" t="inlineStr">
         <is>
           <t>（税抜金額）</t>
@@ -1077,17 +1189,17 @@
           <t>（税抜金額）</t>
         </is>
       </c>
-      <c r="AT15" s="19"/>
+      <c r="AT15" s="6"/>
       <c r="AU15" s="33" t="inlineStr">
         <is>
           <t>（税抜金額）</t>
         </is>
       </c>
-      <c r="AV15" s="19"/>
-      <c r="AW15" s="19"/>
-      <c r="AX15" s="19"/>
-      <c r="AY15" s="19"/>
-      <c r="AZ15" s="20"/>
+      <c r="AV15" s="7"/>
+      <c r="AW15" s="7"/>
+      <c r="AX15" s="7"/>
+      <c r="AY15" s="7"/>
+      <c r="AZ15" s="8"/>
       <c r="BA15" s="32" t="inlineStr">
         <is>
           <t>税率</t>
@@ -1098,189 +1210,325 @@
           <t>税率</t>
         </is>
       </c>
-      <c r="BC15" s="20"/>
-      <c r="BD15" s="10"/>
+      <c r="BC15" s="8"/>
+      <c r="BD15" s="11"/>
       <c r="BE15" s="2"/>
       <c r="BF15" s="3"/>
+      <c r="BG15" s="4"/>
     </row>
     <row r="16">
-      <c r="B16" s="5"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="6"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="6"/>
-      <c r="R16" s="6"/>
-      <c r="S16" s="6"/>
-      <c r="T16" s="6"/>
-      <c r="U16" s="6"/>
-      <c r="V16" s="6"/>
-      <c r="W16" s="6"/>
-      <c r="X16" s="6"/>
-      <c r="Y16" s="6"/>
-      <c r="Z16" s="6"/>
-      <c r="AA16" s="6"/>
-      <c r="AB16" s="6"/>
-      <c r="AC16" s="6"/>
-      <c r="AD16" s="6"/>
-      <c r="AE16" s="7"/>
-      <c r="AF16" s="5"/>
-      <c r="AG16" s="6"/>
-      <c r="AH16" s="7"/>
-      <c r="AI16" s="5"/>
-      <c r="AJ16" s="6"/>
-      <c r="AK16" s="6"/>
-      <c r="AL16" s="6"/>
-      <c r="AM16" s="7"/>
-      <c r="AN16" s="5"/>
-      <c r="AO16" s="6"/>
-      <c r="AP16" s="6"/>
-      <c r="AQ16" s="6"/>
-      <c r="AR16" s="7"/>
-      <c r="BD16" s="5"/>
-      <c r="BE16" s="6"/>
-      <c r="BF16" s="7"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
+      <c r="U16" s="7"/>
+      <c r="V16" s="7"/>
+      <c r="W16" s="7"/>
+      <c r="X16" s="7"/>
+      <c r="Y16" s="7"/>
+      <c r="Z16" s="7"/>
+      <c r="AA16" s="7"/>
+      <c r="AB16" s="7"/>
+      <c r="AC16" s="7"/>
+      <c r="AD16" s="7"/>
+      <c r="AE16" s="8"/>
+      <c r="AF16" s="6"/>
+      <c r="AG16" s="7"/>
+      <c r="AH16" s="8"/>
+      <c r="AI16" s="6"/>
+      <c r="AJ16" s="7"/>
+      <c r="AK16" s="7"/>
+      <c r="AL16" s="7"/>
+      <c r="AM16" s="8"/>
+      <c r="AN16" s="6"/>
+      <c r="AO16" s="7"/>
+      <c r="AP16" s="7"/>
+      <c r="AQ16" s="7"/>
+      <c r="AR16" s="8"/>
+      <c r="AS16" s="6"/>
+      <c r="AT16" s="6"/>
+      <c r="AU16" s="7"/>
+      <c r="AV16" s="7"/>
+      <c r="AW16" s="7"/>
+      <c r="AX16" s="7"/>
+      <c r="AY16" s="7"/>
+      <c r="AZ16" s="8"/>
+      <c r="BA16" s="6"/>
+      <c r="BB16" s="7"/>
+      <c r="BC16" s="8"/>
+      <c r="BD16" s="6"/>
+      <c r="BE16" s="7"/>
+      <c r="BF16" s="8"/>
+      <c r="BG16" s="4"/>
     </row>
     <row r="17">
-      <c r="B17" s="21"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="20"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="20"/>
-      <c r="M17" s="21"/>
-      <c r="N17" s="19"/>
-      <c r="O17" s="19"/>
-      <c r="P17" s="19"/>
-      <c r="Q17" s="19"/>
-      <c r="R17" s="19"/>
-      <c r="S17" s="19"/>
-      <c r="T17" s="19"/>
-      <c r="U17" s="19"/>
-      <c r="V17" s="19"/>
-      <c r="W17" s="19"/>
-      <c r="X17" s="19"/>
-      <c r="Y17" s="19"/>
-      <c r="Z17" s="19"/>
-      <c r="AA17" s="19"/>
-      <c r="AB17" s="19"/>
-      <c r="AC17" s="19"/>
-      <c r="AD17" s="19"/>
-      <c r="AE17" s="20"/>
-      <c r="AF17" s="21"/>
-      <c r="AG17" s="19"/>
-      <c r="AH17" s="20"/>
-      <c r="AI17" s="21"/>
-      <c r="AJ17" s="19"/>
-      <c r="AK17" s="19"/>
-      <c r="AL17" s="19"/>
-      <c r="AM17" s="20"/>
-      <c r="AN17" s="21"/>
-      <c r="AO17" s="19"/>
-      <c r="AP17" s="19"/>
-      <c r="AQ17" s="19"/>
-      <c r="AR17" s="20"/>
-      <c r="AS17" s="21"/>
-      <c r="AT17" s="19"/>
-      <c r="AU17" s="19"/>
-      <c r="AV17" s="19"/>
-      <c r="AW17" s="19"/>
-      <c r="AX17" s="19"/>
-      <c r="AY17" s="19"/>
-      <c r="AZ17" s="20"/>
-      <c r="BA17" s="21"/>
-      <c r="BB17" s="19"/>
-      <c r="BC17" s="20"/>
-      <c r="BD17" s="21"/>
-      <c r="BE17" s="19"/>
-      <c r="BF17" s="20"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
+      <c r="U17" s="7"/>
+      <c r="V17" s="7"/>
+      <c r="W17" s="7"/>
+      <c r="X17" s="7"/>
+      <c r="Y17" s="7"/>
+      <c r="Z17" s="7"/>
+      <c r="AA17" s="7"/>
+      <c r="AB17" s="7"/>
+      <c r="AC17" s="7"/>
+      <c r="AD17" s="7"/>
+      <c r="AE17" s="8"/>
+      <c r="AF17" s="6"/>
+      <c r="AG17" s="7"/>
+      <c r="AH17" s="8"/>
+      <c r="AI17" s="6"/>
+      <c r="AJ17" s="7"/>
+      <c r="AK17" s="7"/>
+      <c r="AL17" s="7"/>
+      <c r="AM17" s="8"/>
+      <c r="AN17" s="6"/>
+      <c r="AO17" s="7"/>
+      <c r="AP17" s="7"/>
+      <c r="AQ17" s="7"/>
+      <c r="AR17" s="8"/>
+      <c r="AS17" s="6"/>
+      <c r="AT17" s="6"/>
+      <c r="AU17" s="7"/>
+      <c r="AV17" s="7"/>
+      <c r="AW17" s="7"/>
+      <c r="AX17" s="7"/>
+      <c r="AY17" s="7"/>
+      <c r="AZ17" s="8"/>
+      <c r="BA17" s="6"/>
+      <c r="BB17" s="7"/>
+      <c r="BC17" s="8"/>
+      <c r="BD17" s="6"/>
+      <c r="BE17" s="7"/>
+      <c r="BF17" s="8"/>
+      <c r="BG17" s="4"/>
     </row>
     <row r="18">
-      <c r="E18" s="21"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="20"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="7"/>
+      <c r="R18" s="7"/>
+      <c r="S18" s="7"/>
+      <c r="T18" s="7"/>
+      <c r="U18" s="7"/>
+      <c r="V18" s="7"/>
+      <c r="W18" s="7"/>
+      <c r="X18" s="7"/>
+      <c r="Y18" s="7"/>
+      <c r="Z18" s="7"/>
+      <c r="AA18" s="7"/>
+      <c r="AB18" s="7"/>
+      <c r="AC18" s="7"/>
+      <c r="AD18" s="7"/>
+      <c r="AE18" s="8"/>
+      <c r="AF18" s="6"/>
+      <c r="AG18" s="7"/>
+      <c r="AH18" s="8"/>
+      <c r="AI18" s="6"/>
+      <c r="AJ18" s="7"/>
+      <c r="AK18" s="7"/>
+      <c r="AL18" s="7"/>
+      <c r="AM18" s="8"/>
+      <c r="AN18" s="6"/>
+      <c r="AO18" s="7"/>
+      <c r="AP18" s="7"/>
+      <c r="AQ18" s="7"/>
+      <c r="AR18" s="8"/>
+      <c r="AS18" s="6"/>
+      <c r="AT18" s="6"/>
+      <c r="AU18" s="7"/>
+      <c r="AV18" s="7"/>
+      <c r="AW18" s="7"/>
+      <c r="AX18" s="7"/>
+      <c r="AY18" s="7"/>
+      <c r="AZ18" s="8"/>
+      <c r="BA18" s="6"/>
+      <c r="BB18" s="7"/>
+      <c r="BC18" s="8"/>
+      <c r="BD18" s="6"/>
+      <c r="BE18" s="7"/>
+      <c r="BF18" s="8"/>
+      <c r="BG18" s="4"/>
     </row>
     <row r="19">
-      <c r="B19" s="21"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="20"/>
-      <c r="J19" s="21"/>
-      <c r="K19" s="19"/>
-      <c r="L19" s="20"/>
-      <c r="M19" s="21"/>
-      <c r="N19" s="19"/>
-      <c r="O19" s="19"/>
-      <c r="P19" s="19"/>
-      <c r="Q19" s="19"/>
-      <c r="R19" s="19"/>
-      <c r="S19" s="19"/>
-      <c r="T19" s="19"/>
-      <c r="U19" s="19"/>
-      <c r="V19" s="19"/>
-      <c r="W19" s="19"/>
-      <c r="X19" s="19"/>
-      <c r="Y19" s="19"/>
-      <c r="Z19" s="19"/>
-      <c r="AA19" s="19"/>
-      <c r="AB19" s="19"/>
-      <c r="AC19" s="19"/>
-      <c r="AD19" s="19"/>
-      <c r="AE19" s="20"/>
-      <c r="AF19" s="21"/>
-      <c r="AG19" s="19"/>
-      <c r="AH19" s="20"/>
-      <c r="AI19" s="21"/>
-      <c r="AJ19" s="19"/>
-      <c r="AK19" s="19"/>
-      <c r="AL19" s="19"/>
-      <c r="AM19" s="20"/>
-      <c r="AN19" s="21"/>
-      <c r="AO19" s="19"/>
-      <c r="AP19" s="19"/>
-      <c r="AQ19" s="19"/>
-      <c r="AR19" s="20"/>
-      <c r="AS19" s="21"/>
-      <c r="AT19" s="19"/>
-      <c r="AU19" s="19"/>
-      <c r="AV19" s="19"/>
-      <c r="AW19" s="19"/>
-      <c r="AX19" s="19"/>
-      <c r="AY19" s="19"/>
-      <c r="AZ19" s="20"/>
-      <c r="BA19" s="21"/>
-      <c r="BB19" s="19"/>
-      <c r="BC19" s="20"/>
-      <c r="BD19" s="21"/>
-      <c r="BE19" s="19"/>
-      <c r="BF19" s="20"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="7"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="7"/>
+      <c r="R19" s="7"/>
+      <c r="S19" s="7"/>
+      <c r="T19" s="7"/>
+      <c r="U19" s="7"/>
+      <c r="V19" s="7"/>
+      <c r="W19" s="7"/>
+      <c r="X19" s="7"/>
+      <c r="Y19" s="7"/>
+      <c r="Z19" s="7"/>
+      <c r="AA19" s="7"/>
+      <c r="AB19" s="7"/>
+      <c r="AC19" s="7"/>
+      <c r="AD19" s="7"/>
+      <c r="AE19" s="8"/>
+      <c r="AF19" s="6"/>
+      <c r="AG19" s="7"/>
+      <c r="AH19" s="8"/>
+      <c r="AI19" s="6"/>
+      <c r="AJ19" s="7"/>
+      <c r="AK19" s="7"/>
+      <c r="AL19" s="7"/>
+      <c r="AM19" s="8"/>
+      <c r="AN19" s="6"/>
+      <c r="AO19" s="7"/>
+      <c r="AP19" s="7"/>
+      <c r="AQ19" s="7"/>
+      <c r="AR19" s="8"/>
+      <c r="AS19" s="6"/>
+      <c r="AT19" s="6"/>
+      <c r="AU19" s="7"/>
+      <c r="AV19" s="7"/>
+      <c r="AW19" s="7"/>
+      <c r="AX19" s="7"/>
+      <c r="AY19" s="7"/>
+      <c r="AZ19" s="8"/>
+      <c r="BA19" s="6"/>
+      <c r="BB19" s="7"/>
+      <c r="BC19" s="8"/>
+      <c r="BD19" s="6"/>
+      <c r="BE19" s="7"/>
+      <c r="BF19" s="8"/>
+      <c r="BG19" s="4"/>
     </row>
     <row r="20">
-      <c r="E20" s="21"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="20"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="7"/>
+      <c r="O20" s="7"/>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="7"/>
+      <c r="R20" s="7"/>
+      <c r="S20" s="7"/>
+      <c r="T20" s="7"/>
+      <c r="U20" s="7"/>
+      <c r="V20" s="7"/>
+      <c r="W20" s="7"/>
+      <c r="X20" s="7"/>
+      <c r="Y20" s="7"/>
+      <c r="Z20" s="7"/>
+      <c r="AA20" s="7"/>
+      <c r="AB20" s="7"/>
+      <c r="AC20" s="7"/>
+      <c r="AD20" s="7"/>
+      <c r="AE20" s="8"/>
+      <c r="AF20" s="6"/>
+      <c r="AG20" s="7"/>
+      <c r="AH20" s="8"/>
+      <c r="AI20" s="6"/>
+      <c r="AJ20" s="7"/>
+      <c r="AK20" s="7"/>
+      <c r="AL20" s="7"/>
+      <c r="AM20" s="8"/>
+      <c r="AN20" s="6"/>
+      <c r="AO20" s="7"/>
+      <c r="AP20" s="7"/>
+      <c r="AQ20" s="7"/>
+      <c r="AR20" s="8"/>
+      <c r="AS20" s="6"/>
+      <c r="AT20" s="6"/>
+      <c r="AU20" s="7"/>
+      <c r="AV20" s="7"/>
+      <c r="AW20" s="7"/>
+      <c r="AX20" s="7"/>
+      <c r="AY20" s="7"/>
+      <c r="AZ20" s="8"/>
+      <c r="BA20" s="6"/>
+      <c r="BB20" s="7"/>
+      <c r="BC20" s="8"/>
+      <c r="BD20" s="6"/>
+      <c r="BE20" s="7"/>
+      <c r="BF20" s="8"/>
+      <c r="BG20" s="4"/>
     </row>
     <row r="21">
-      <c r="B21" s="10"/>
+      <c r="B21" s="11"/>
       <c r="C21" s="2"/>
       <c r="D21" s="3"/>
-      <c r="J21" s="10"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="11"/>
       <c r="K21" s="2"/>
       <c r="L21" s="3"/>
-      <c r="M21" s="10"/>
+      <c r="M21" s="11"/>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
@@ -1299,243 +1547,361 @@
       <c r="AC21" s="2"/>
       <c r="AD21" s="2"/>
       <c r="AE21" s="3"/>
-      <c r="AF21" s="10"/>
+      <c r="AF21" s="11"/>
       <c r="AG21" s="2"/>
       <c r="AH21" s="3"/>
-      <c r="AI21" s="10"/>
+      <c r="AI21" s="11"/>
       <c r="AJ21" s="2"/>
       <c r="AK21" s="2"/>
       <c r="AL21" s="2"/>
       <c r="AM21" s="3"/>
-      <c r="AN21" s="10"/>
+      <c r="AN21" s="11"/>
       <c r="AO21" s="2"/>
       <c r="AP21" s="2"/>
       <c r="AQ21" s="2"/>
       <c r="AR21" s="3"/>
-      <c r="AS21" s="10"/>
-      <c r="AT21" s="2"/>
+      <c r="AS21" s="11"/>
+      <c r="AT21" s="11"/>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
       <c r="AX21" s="2"/>
       <c r="AY21" s="2"/>
       <c r="AZ21" s="3"/>
-      <c r="BA21" s="10"/>
+      <c r="BA21" s="11"/>
       <c r="BB21" s="2"/>
       <c r="BC21" s="3"/>
-      <c r="BD21" s="10"/>
+      <c r="BD21" s="11"/>
       <c r="BE21" s="2"/>
       <c r="BF21" s="3"/>
+      <c r="BG21" s="4"/>
     </row>
     <row r="22">
-      <c r="B22" s="5"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="5"/>
-      <c r="N22" s="6"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
-      <c r="Q22" s="6"/>
-      <c r="R22" s="6"/>
-      <c r="S22" s="6"/>
-      <c r="T22" s="6"/>
-      <c r="U22" s="6"/>
-      <c r="V22" s="6"/>
-      <c r="W22" s="6"/>
-      <c r="X22" s="6"/>
-      <c r="Y22" s="6"/>
-      <c r="Z22" s="6"/>
-      <c r="AA22" s="6"/>
-      <c r="AB22" s="6"/>
-      <c r="AC22" s="6"/>
-      <c r="AD22" s="6"/>
-      <c r="AE22" s="7"/>
-      <c r="AF22" s="5"/>
-      <c r="AG22" s="6"/>
-      <c r="AH22" s="7"/>
-      <c r="AI22" s="5"/>
-      <c r="AJ22" s="6"/>
-      <c r="AK22" s="6"/>
-      <c r="AL22" s="6"/>
-      <c r="AM22" s="7"/>
-      <c r="AN22" s="5"/>
-      <c r="AO22" s="6"/>
-      <c r="AP22" s="6"/>
-      <c r="AQ22" s="6"/>
-      <c r="AR22" s="7"/>
-      <c r="AS22" s="5"/>
-      <c r="AT22" s="6"/>
-      <c r="AU22" s="6"/>
-      <c r="AV22" s="6"/>
-      <c r="AW22" s="6"/>
-      <c r="AX22" s="6"/>
-      <c r="AY22" s="6"/>
-      <c r="AZ22" s="7"/>
-      <c r="BA22" s="5"/>
-      <c r="BB22" s="6"/>
-      <c r="BC22" s="7"/>
-      <c r="BD22" s="5"/>
-      <c r="BE22" s="6"/>
-      <c r="BF22" s="7"/>
+      <c r="B22" s="34"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="35"/>
+      <c r="L22" s="36"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="35"/>
+      <c r="O22" s="35"/>
+      <c r="P22" s="35"/>
+      <c r="Q22" s="35"/>
+      <c r="R22" s="35"/>
+      <c r="S22" s="35"/>
+      <c r="T22" s="35"/>
+      <c r="U22" s="35"/>
+      <c r="V22" s="35"/>
+      <c r="W22" s="35"/>
+      <c r="X22" s="35"/>
+      <c r="Y22" s="35"/>
+      <c r="Z22" s="35"/>
+      <c r="AA22" s="35"/>
+      <c r="AB22" s="35"/>
+      <c r="AC22" s="35"/>
+      <c r="AD22" s="35"/>
+      <c r="AE22" s="36"/>
+      <c r="AF22" s="34"/>
+      <c r="AG22" s="35"/>
+      <c r="AH22" s="36"/>
+      <c r="AI22" s="34"/>
+      <c r="AJ22" s="35"/>
+      <c r="AK22" s="35"/>
+      <c r="AL22" s="35"/>
+      <c r="AM22" s="36"/>
+      <c r="AN22" s="34"/>
+      <c r="AO22" s="35"/>
+      <c r="AP22" s="35"/>
+      <c r="AQ22" s="35"/>
+      <c r="AR22" s="36"/>
+      <c r="AS22" s="34"/>
+      <c r="AT22" s="34"/>
+      <c r="AU22" s="35"/>
+      <c r="AV22" s="35"/>
+      <c r="AW22" s="35"/>
+      <c r="AX22" s="35"/>
+      <c r="AY22" s="35"/>
+      <c r="AZ22" s="36"/>
+      <c r="BA22" s="34"/>
+      <c r="BB22" s="35"/>
+      <c r="BC22" s="36"/>
+      <c r="BD22" s="34"/>
+      <c r="BE22" s="35"/>
+      <c r="BF22" s="36"/>
+      <c r="BG22" s="4"/>
     </row>
     <row r="23">
-      <c r="B23" s="21"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19"/>
-      <c r="L23" s="19"/>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19"/>
-      <c r="P23" s="19"/>
-      <c r="Q23" s="19"/>
-      <c r="R23" s="19"/>
-      <c r="S23" s="19"/>
-      <c r="T23" s="19"/>
-      <c r="U23" s="19"/>
-      <c r="V23" s="19"/>
-      <c r="W23" s="19"/>
-      <c r="X23" s="19"/>
-      <c r="Y23" s="19"/>
-      <c r="Z23" s="19"/>
-      <c r="AA23" s="19"/>
-      <c r="AB23" s="19"/>
-      <c r="AC23" s="19"/>
-      <c r="AD23" s="19"/>
-      <c r="AE23" s="19"/>
-      <c r="AF23" s="19"/>
-      <c r="AG23" s="19"/>
-      <c r="AH23" s="19"/>
-      <c r="AI23" s="19"/>
-      <c r="AJ23" s="19"/>
-      <c r="AK23" s="19"/>
-      <c r="AL23" s="19"/>
-      <c r="AM23" s="20"/>
-      <c r="AN23" s="21"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="7"/>
+      <c r="O23" s="7"/>
+      <c r="P23" s="7"/>
+      <c r="Q23" s="7"/>
+      <c r="R23" s="7"/>
+      <c r="S23" s="7"/>
+      <c r="T23" s="7"/>
+      <c r="U23" s="7"/>
+      <c r="V23" s="7"/>
+      <c r="W23" s="7"/>
+      <c r="X23" s="7"/>
+      <c r="Y23" s="7"/>
+      <c r="Z23" s="7"/>
+      <c r="AA23" s="7"/>
+      <c r="AB23" s="7"/>
+      <c r="AC23" s="7"/>
+      <c r="AD23" s="7"/>
+      <c r="AE23" s="7"/>
+      <c r="AF23" s="6"/>
+      <c r="AG23" s="7"/>
+      <c r="AH23" s="7"/>
+      <c r="AI23" s="6"/>
+      <c r="AJ23" s="7"/>
+      <c r="AK23" s="7"/>
+      <c r="AL23" s="7"/>
+      <c r="AM23" s="8"/>
+      <c r="AN23" s="6"/>
       <c r="AO23" s="33" t="inlineStr">
         <is>
           <t>（税抜金額）</t>
         </is>
       </c>
-      <c r="AP23" s="19"/>
-      <c r="AQ23" s="19"/>
-      <c r="AR23" s="20"/>
-      <c r="AS23" s="21"/>
-      <c r="AT23" s="33" t="inlineStr">
+      <c r="AP23" s="7"/>
+      <c r="AQ23" s="7"/>
+      <c r="AR23" s="8"/>
+      <c r="AS23" s="6"/>
+      <c r="AT23" s="37" t="inlineStr">
         <is>
           <t>(消費税)</t>
         </is>
       </c>
-      <c r="AU23" s="19"/>
-      <c r="AV23" s="19"/>
-      <c r="AW23" s="20"/>
-      <c r="AX23" s="21"/>
+      <c r="AU23" s="7"/>
+      <c r="AV23" s="7"/>
+      <c r="AW23" s="8"/>
+      <c r="AX23" s="6"/>
       <c r="AY23" s="33" t="inlineStr">
         <is>
           <t>(税込金額)</t>
         </is>
       </c>
-      <c r="AZ23" s="19"/>
-      <c r="BA23" s="19"/>
-      <c r="BB23" s="19"/>
-      <c r="BC23" s="20"/>
-      <c r="BD23" s="21"/>
-      <c r="BE23" s="19"/>
-      <c r="BF23" s="20"/>
+      <c r="AZ23" s="7"/>
+      <c r="BA23" s="6"/>
+      <c r="BB23" s="7"/>
+      <c r="BC23" s="8"/>
+      <c r="BD23" s="6"/>
+      <c r="BE23" s="7"/>
+      <c r="BF23" s="8"/>
+      <c r="BG23" s="4"/>
     </row>
     <row r="24">
-      <c r="AH24" s="9" t="inlineStr">
+      <c r="B24" s="6"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
+      <c r="O24" s="7"/>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="7"/>
+      <c r="R24" s="7"/>
+      <c r="S24" s="7"/>
+      <c r="T24" s="7"/>
+      <c r="U24" s="7"/>
+      <c r="V24" s="7"/>
+      <c r="W24" s="7"/>
+      <c r="X24" s="7"/>
+      <c r="Y24" s="7"/>
+      <c r="Z24" s="7"/>
+      <c r="AA24" s="7"/>
+      <c r="AB24" s="7"/>
+      <c r="AC24" s="7"/>
+      <c r="AD24" s="7"/>
+      <c r="AE24" s="7"/>
+      <c r="AF24" s="7"/>
+      <c r="AG24" s="7"/>
+      <c r="AH24" s="33" t="inlineStr">
         <is>
           <t>非・不課税小計</t>
         </is>
       </c>
+      <c r="AI24" s="7"/>
+      <c r="AJ24" s="7"/>
+      <c r="AK24" s="7"/>
+      <c r="AL24" s="7"/>
+      <c r="AM24" s="8"/>
+      <c r="AN24" s="6"/>
+      <c r="AO24" s="7"/>
+      <c r="AP24" s="7"/>
+      <c r="AQ24" s="7"/>
+      <c r="AR24" s="8"/>
+      <c r="AS24" s="6"/>
+      <c r="AT24" s="7"/>
+      <c r="AU24" s="7"/>
+      <c r="AV24" s="7"/>
+      <c r="AW24" s="8"/>
+      <c r="AX24" s="6"/>
+      <c r="AY24" s="7"/>
+      <c r="AZ24" s="7"/>
+      <c r="BA24" s="7"/>
+      <c r="BB24" s="7"/>
+      <c r="BC24" s="8"/>
+      <c r="BD24" s="6"/>
+      <c r="BE24" s="7"/>
+      <c r="BF24" s="8"/>
+      <c r="BG24" s="4"/>
     </row>
     <row r="25">
-      <c r="B25" s="21"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
-      <c r="L25" s="19"/>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19"/>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="19"/>
-      <c r="R25" s="19"/>
-      <c r="S25" s="19"/>
-      <c r="T25" s="19"/>
-      <c r="U25" s="19"/>
-      <c r="V25" s="19"/>
-      <c r="W25" s="19"/>
-      <c r="X25" s="19"/>
-      <c r="Y25" s="19"/>
-      <c r="Z25" s="19"/>
-      <c r="AA25" s="19"/>
-      <c r="AB25" s="19"/>
-      <c r="AC25" s="19"/>
-      <c r="AD25" s="19"/>
-      <c r="AE25" s="19"/>
-      <c r="AF25" s="19"/>
-      <c r="AG25" s="19"/>
-      <c r="AH25" s="19"/>
-      <c r="AI25" s="19"/>
-      <c r="AJ25" s="19"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
+      <c r="O25" s="7"/>
+      <c r="P25" s="7"/>
+      <c r="Q25" s="7"/>
+      <c r="R25" s="7"/>
+      <c r="S25" s="7"/>
+      <c r="T25" s="7"/>
+      <c r="U25" s="7"/>
+      <c r="V25" s="7"/>
+      <c r="W25" s="7"/>
+      <c r="X25" s="7"/>
+      <c r="Y25" s="7"/>
+      <c r="Z25" s="7"/>
+      <c r="AA25" s="7"/>
+      <c r="AB25" s="7"/>
+      <c r="AC25" s="7"/>
+      <c r="AD25" s="7"/>
+      <c r="AE25" s="7"/>
+      <c r="AF25" s="7"/>
+      <c r="AG25" s="7"/>
+      <c r="AH25" s="7"/>
+      <c r="AI25" s="7"/>
+      <c r="AJ25" s="7"/>
       <c r="AK25" s="33" t="inlineStr">
         <is>
           <t>8%小計</t>
         </is>
       </c>
-      <c r="AL25" s="19"/>
-      <c r="AM25" s="20"/>
-      <c r="AN25" s="21"/>
-      <c r="AO25" s="19"/>
-      <c r="AP25" s="19"/>
-      <c r="AQ25" s="19"/>
-      <c r="AR25" s="20"/>
-      <c r="AS25" s="21"/>
-      <c r="AT25" s="19"/>
-      <c r="AU25" s="19"/>
-      <c r="AV25" s="19"/>
-      <c r="AW25" s="20"/>
-      <c r="AX25" s="21"/>
-      <c r="AY25" s="19"/>
-      <c r="AZ25" s="19"/>
-      <c r="BA25" s="19"/>
-      <c r="BB25" s="19"/>
-      <c r="BC25" s="20"/>
-      <c r="BD25" s="21"/>
-      <c r="BE25" s="19"/>
-      <c r="BF25" s="20"/>
+      <c r="AL25" s="7"/>
+      <c r="AM25" s="8"/>
+      <c r="AN25" s="6"/>
+      <c r="AO25" s="7"/>
+      <c r="AP25" s="7"/>
+      <c r="AQ25" s="7"/>
+      <c r="AR25" s="8"/>
+      <c r="AS25" s="6"/>
+      <c r="AT25" s="7"/>
+      <c r="AU25" s="7"/>
+      <c r="AV25" s="7"/>
+      <c r="AW25" s="8"/>
+      <c r="AX25" s="6"/>
+      <c r="AY25" s="7"/>
+      <c r="AZ25" s="7"/>
+      <c r="BA25" s="7"/>
+      <c r="BB25" s="7"/>
+      <c r="BC25" s="8"/>
+      <c r="BD25" s="6"/>
+      <c r="BE25" s="7"/>
+      <c r="BF25" s="8"/>
+      <c r="BG25" s="4"/>
     </row>
     <row r="26">
-      <c r="AJ26" s="9" t="inlineStr">
+      <c r="B26" s="6"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="7"/>
+      <c r="O26" s="7"/>
+      <c r="P26" s="7"/>
+      <c r="Q26" s="7"/>
+      <c r="R26" s="7"/>
+      <c r="S26" s="7"/>
+      <c r="T26" s="7"/>
+      <c r="U26" s="7"/>
+      <c r="V26" s="7"/>
+      <c r="W26" s="7"/>
+      <c r="X26" s="7"/>
+      <c r="Y26" s="7"/>
+      <c r="Z26" s="7"/>
+      <c r="AA26" s="7"/>
+      <c r="AB26" s="7"/>
+      <c r="AC26" s="7"/>
+      <c r="AD26" s="7"/>
+      <c r="AE26" s="7"/>
+      <c r="AF26" s="7"/>
+      <c r="AG26" s="7"/>
+      <c r="AH26" s="7"/>
+      <c r="AI26" s="7"/>
+      <c r="AJ26" s="33" t="inlineStr">
         <is>
           <t>10%小計</t>
         </is>
       </c>
+      <c r="AK26" s="7"/>
+      <c r="AL26" s="7"/>
+      <c r="AM26" s="8"/>
+      <c r="AN26" s="6"/>
+      <c r="AO26" s="7"/>
+      <c r="AP26" s="7"/>
+      <c r="AQ26" s="7"/>
+      <c r="AR26" s="8"/>
+      <c r="AS26" s="6"/>
+      <c r="AT26" s="7"/>
+      <c r="AU26" s="7"/>
+      <c r="AV26" s="7"/>
+      <c r="AW26" s="8"/>
+      <c r="AX26" s="6"/>
+      <c r="AY26" s="7"/>
+      <c r="AZ26" s="7"/>
+      <c r="BA26" s="7"/>
+      <c r="BB26" s="7"/>
+      <c r="BC26" s="8"/>
+      <c r="BD26" s="6"/>
+      <c r="BE26" s="7"/>
+      <c r="BF26" s="8"/>
+      <c r="BG26" s="4"/>
     </row>
     <row r="27">
-      <c r="B27" s="10"/>
+      <c r="B27" s="11"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
@@ -1573,157 +1939,234 @@
       <c r="AK27" s="2"/>
       <c r="AL27" s="2"/>
       <c r="AM27" s="3"/>
-      <c r="AN27" s="10"/>
+      <c r="AN27" s="11"/>
       <c r="AO27" s="2"/>
       <c r="AP27" s="2"/>
       <c r="AQ27" s="2"/>
       <c r="AR27" s="3"/>
-      <c r="AS27" s="10"/>
+      <c r="AS27" s="11"/>
       <c r="AT27" s="2"/>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="3"/>
-      <c r="AX27" s="10"/>
+      <c r="AX27" s="11"/>
       <c r="AY27" s="2"/>
       <c r="AZ27" s="2"/>
       <c r="BA27" s="2"/>
       <c r="BB27" s="2"/>
       <c r="BC27" s="3"/>
-      <c r="BD27" s="10"/>
+      <c r="BD27" s="11"/>
       <c r="BE27" s="2"/>
       <c r="BF27" s="3"/>
+      <c r="BG27" s="4"/>
     </row>
     <row r="28">
-      <c r="B28" s="5"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
-      <c r="M28" s="6"/>
-      <c r="N28" s="6"/>
-      <c r="O28" s="6"/>
-      <c r="P28" s="6"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="6"/>
-      <c r="S28" s="6"/>
-      <c r="T28" s="6"/>
-      <c r="U28" s="6"/>
-      <c r="V28" s="6"/>
-      <c r="W28" s="6"/>
-      <c r="X28" s="6"/>
-      <c r="Y28" s="6"/>
-      <c r="Z28" s="6"/>
-      <c r="AA28" s="6"/>
-      <c r="AB28" s="6"/>
-      <c r="AC28" s="6"/>
-      <c r="AD28" s="6"/>
-      <c r="AE28" s="6"/>
-      <c r="AF28" s="6"/>
-      <c r="AG28" s="6"/>
-      <c r="AH28" s="6"/>
-      <c r="AI28" s="6"/>
-      <c r="AJ28" s="6"/>
-      <c r="AK28" s="34" t="inlineStr">
+      <c r="B28" s="34"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="35"/>
+      <c r="I28" s="35"/>
+      <c r="J28" s="35"/>
+      <c r="K28" s="35"/>
+      <c r="L28" s="35"/>
+      <c r="M28" s="35"/>
+      <c r="N28" s="35"/>
+      <c r="O28" s="35"/>
+      <c r="P28" s="35"/>
+      <c r="Q28" s="35"/>
+      <c r="R28" s="35"/>
+      <c r="S28" s="35"/>
+      <c r="T28" s="35"/>
+      <c r="U28" s="35"/>
+      <c r="V28" s="35"/>
+      <c r="W28" s="35"/>
+      <c r="X28" s="35"/>
+      <c r="Y28" s="35"/>
+      <c r="Z28" s="35"/>
+      <c r="AA28" s="35"/>
+      <c r="AB28" s="35"/>
+      <c r="AC28" s="35"/>
+      <c r="AD28" s="35"/>
+      <c r="AE28" s="35"/>
+      <c r="AF28" s="35"/>
+      <c r="AG28" s="35"/>
+      <c r="AH28" s="35"/>
+      <c r="AI28" s="35"/>
+      <c r="AJ28" s="35"/>
+      <c r="AK28" s="38" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="AL28" s="6"/>
-      <c r="AM28" s="7"/>
-      <c r="AN28" s="5"/>
-      <c r="AO28" s="6"/>
-      <c r="AP28" s="6"/>
-      <c r="AQ28" s="6"/>
-      <c r="AR28" s="7"/>
-      <c r="AS28" s="5"/>
-      <c r="AT28" s="6"/>
-      <c r="AU28" s="6"/>
-      <c r="AV28" s="6"/>
-      <c r="AW28" s="7"/>
-      <c r="AX28" s="5"/>
-      <c r="AY28" s="6"/>
-      <c r="AZ28" s="6"/>
-      <c r="BA28" s="6"/>
-      <c r="BB28" s="6"/>
-      <c r="BC28" s="7"/>
-      <c r="BD28" s="5"/>
-      <c r="BE28" s="6"/>
-      <c r="BF28" s="7"/>
+      <c r="AL28" s="35"/>
+      <c r="AM28" s="36"/>
+      <c r="AN28" s="34"/>
+      <c r="AO28" s="35"/>
+      <c r="AP28" s="35"/>
+      <c r="AQ28" s="35"/>
+      <c r="AR28" s="36"/>
+      <c r="AS28" s="34"/>
+      <c r="AT28" s="35"/>
+      <c r="AU28" s="35"/>
+      <c r="AV28" s="35"/>
+      <c r="AW28" s="36"/>
+      <c r="AX28" s="34"/>
+      <c r="AY28" s="35"/>
+      <c r="AZ28" s="35"/>
+      <c r="BA28" s="35"/>
+      <c r="BB28" s="35"/>
+      <c r="BC28" s="36"/>
+      <c r="BD28" s="34"/>
+      <c r="BE28" s="35"/>
+      <c r="BF28" s="36"/>
+      <c r="BG28" s="4"/>
     </row>
     <row r="29">
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B29" s="39" t="inlineStr">
         <is>
           <t>※提出部数</t>
         </is>
       </c>
-      <c r="F29" s="16" t="inlineStr">
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="40" t="inlineStr">
         <is>
           <t>1部（白黒で構いません）・・・毎月５日必着</t>
         </is>
       </c>
-      <c r="AN29" s="35" t="inlineStr">
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="2"/>
+      <c r="T29" s="2"/>
+      <c r="U29" s="2"/>
+      <c r="V29" s="2"/>
+      <c r="W29" s="2"/>
+      <c r="X29" s="2"/>
+      <c r="Y29" s="2"/>
+      <c r="Z29" s="2"/>
+      <c r="AA29" s="2"/>
+      <c r="AB29" s="2"/>
+      <c r="AC29" s="2"/>
+      <c r="AD29" s="2"/>
+      <c r="AE29" s="2"/>
+      <c r="AF29" s="2"/>
+      <c r="AG29" s="2"/>
+      <c r="AH29" s="2"/>
+      <c r="AI29" s="2"/>
+      <c r="AJ29" s="2"/>
+      <c r="AK29" s="2"/>
+      <c r="AL29" s="2"/>
+      <c r="AM29" s="2"/>
+      <c r="AN29" s="41" t="inlineStr">
         <is>
           <t>経営管理部長</t>
         </is>
       </c>
-      <c r="AO29" s="19"/>
-      <c r="AP29" s="20"/>
-      <c r="AQ29" s="21"/>
-      <c r="AR29" s="19"/>
-      <c r="AS29" s="19"/>
-      <c r="AT29" s="19"/>
-      <c r="AU29" s="19"/>
-      <c r="AV29" s="36" t="inlineStr">
+      <c r="AO29" s="7"/>
+      <c r="AP29" s="8"/>
+      <c r="AQ29" s="6"/>
+      <c r="AR29" s="7"/>
+      <c r="AS29" s="6"/>
+      <c r="AT29" s="7"/>
+      <c r="AU29" s="7"/>
+      <c r="AV29" s="42" t="inlineStr">
         <is>
           <t>検</t>
         </is>
       </c>
-      <c r="AW29" s="19"/>
-      <c r="AX29" s="19"/>
-      <c r="AY29" s="36" t="inlineStr">
+      <c r="AW29" s="7"/>
+      <c r="AX29" s="6"/>
+      <c r="AY29" s="42" t="inlineStr">
         <is>
           <t>印</t>
         </is>
       </c>
-      <c r="AZ29" s="19"/>
-      <c r="BA29" s="19"/>
-      <c r="BB29" s="19"/>
-      <c r="BC29" s="20"/>
-      <c r="BD29" s="21"/>
-      <c r="BE29" s="36" t="inlineStr">
+      <c r="AZ29" s="7"/>
+      <c r="BA29" s="7"/>
+      <c r="BB29" s="7"/>
+      <c r="BC29" s="8"/>
+      <c r="BD29" s="6"/>
+      <c r="BE29" s="42" t="inlineStr">
         <is>
           <t>入力者</t>
         </is>
       </c>
-      <c r="BF29" s="20"/>
+      <c r="BF29" s="8"/>
+      <c r="BG29" s="4"/>
     </row>
     <row r="30">
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr">
         <is>
           <t>※毎年１２月のみ２０日締切（２５日必着）翌月末日支払いとさせていただきます。</t>
         </is>
       </c>
-      <c r="AQ30" s="21"/>
-      <c r="AR30" s="19"/>
-      <c r="AS30" s="19"/>
-      <c r="AT30" s="20"/>
-      <c r="AU30" s="21"/>
-      <c r="AV30" s="19"/>
-      <c r="AW30" s="20"/>
-      <c r="AX30" s="21"/>
-      <c r="AY30" s="19"/>
-      <c r="AZ30" s="20"/>
-      <c r="BA30" s="21"/>
-      <c r="BB30" s="19"/>
-      <c r="BC30" s="20"/>
+      <c r="AN30" s="6"/>
+      <c r="AO30" s="7"/>
+      <c r="AP30" s="8"/>
+      <c r="AQ30" s="6"/>
+      <c r="AR30" s="7"/>
+      <c r="AS30" s="7"/>
+      <c r="AT30" s="8"/>
+      <c r="AU30" s="6"/>
+      <c r="AV30" s="7"/>
+      <c r="AW30" s="8"/>
+      <c r="AX30" s="6"/>
+      <c r="AY30" s="7"/>
+      <c r="AZ30" s="8"/>
+      <c r="BA30" s="6"/>
+      <c r="BB30" s="7"/>
+      <c r="BC30" s="8"/>
+      <c r="BD30" s="6"/>
+      <c r="BE30" s="7"/>
+      <c r="BF30" s="8"/>
+      <c r="BG30" s="4"/>
+    </row>
+    <row r="31">
+      <c r="AN31" s="2"/>
+      <c r="AO31" s="2"/>
+      <c r="AP31" s="2"/>
+      <c r="AQ31" s="2"/>
+      <c r="AR31" s="2"/>
+      <c r="AS31" s="2"/>
+      <c r="AT31" s="2"/>
+      <c r="AU31" s="2"/>
+      <c r="AV31" s="2"/>
+      <c r="AW31" s="2"/>
+      <c r="AX31" s="2"/>
+      <c r="AY31" s="2"/>
+      <c r="AZ31" s="2"/>
+      <c r="BA31" s="2"/>
+      <c r="BB31" s="2"/>
+      <c r="BC31" s="2"/>
+      <c r="BD31" s="2"/>
+      <c r="BE31" s="2"/>
+      <c r="BF31" s="2"/>
     </row>
     <row r="33">
+      <c r="AN33" s="11"/>
+      <c r="AO33" s="2"/>
+      <c r="AP33" s="2"/>
+      <c r="AQ33" s="11"/>
+      <c r="AR33" s="2"/>
+      <c r="AS33" s="2"/>
+      <c r="AT33" s="2"/>
+      <c r="AU33" s="11"/>
+      <c r="AV33" s="2"/>
+      <c r="AW33" s="2"/>
       <c r="AX33" s="1" t="inlineStr">
         <is>
           <t>日付(西暦)</t>
@@ -1731,94 +2174,96 @@
       </c>
       <c r="AY33" s="2"/>
       <c r="AZ33" s="2"/>
-      <c r="BA33" s="2"/>
+      <c r="BA33" s="11"/>
       <c r="BB33" s="2"/>
       <c r="BC33" s="2"/>
-      <c r="BD33" s="2"/>
+      <c r="BD33" s="11"/>
       <c r="BE33" s="2"/>
       <c r="BF33" s="3"/>
+      <c r="BG33" s="4"/>
     </row>
     <row r="34">
-      <c r="Z34" s="4" t="inlineStr">
+      <c r="Z34" s="5" t="inlineStr">
         <is>
           <t>請</t>
         </is>
       </c>
-      <c r="AC34" s="4" t="inlineStr">
+      <c r="AC34" s="5" t="inlineStr">
         <is>
           <t>求</t>
         </is>
       </c>
-      <c r="AE34" s="4" t="inlineStr">
+      <c r="AE34" s="5" t="inlineStr">
         <is>
           <t>書</t>
         </is>
       </c>
-      <c r="AG34" s="4" t="inlineStr">
+      <c r="AG34" s="5" t="inlineStr">
         <is>
           <t>(控)</t>
         </is>
       </c>
-      <c r="AX34" s="5"/>
-      <c r="AY34" s="6"/>
-      <c r="AZ34" s="6"/>
-      <c r="BA34" s="6"/>
-      <c r="BB34" s="6"/>
-      <c r="BC34" s="6"/>
-      <c r="BD34" s="6"/>
-      <c r="BE34" s="6"/>
-      <c r="BF34" s="7"/>
+      <c r="AX34" s="6"/>
+      <c r="AY34" s="7"/>
+      <c r="AZ34" s="7"/>
+      <c r="BA34" s="7"/>
+      <c r="BB34" s="7"/>
+      <c r="BC34" s="7"/>
+      <c r="BD34" s="7"/>
+      <c r="BE34" s="7"/>
+      <c r="BF34" s="8"/>
+      <c r="BG34" s="4"/>
     </row>
     <row r="35">
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>グリーン産業株式会社</t>
         </is>
       </c>
-      <c r="K35" s="8" t="inlineStr">
+      <c r="K35" s="9" t="inlineStr">
         <is>
           <t>御中</t>
         </is>
       </c>
-      <c r="AO35" s="9" t="inlineStr">
+      <c r="AO35" s="10" t="inlineStr">
         <is>
           <t>取引先コード</t>
         </is>
       </c>
-      <c r="AS35" s="10"/>
-      <c r="AT35" s="2"/>
+      <c r="AS35" s="11"/>
+      <c r="AT35" s="11"/>
       <c r="AU35" s="2"/>
       <c r="AV35" s="2"/>
       <c r="AW35" s="2"/>
       <c r="AX35" s="2"/>
       <c r="AY35" s="2"/>
       <c r="AZ35" s="2"/>
-      <c r="BA35" s="3"/>
+      <c r="BA35" s="12"/>
     </row>
     <row r="36">
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B36" s="13" t="inlineStr">
         <is>
           <t>下記のとおり請求致します。</t>
         </is>
       </c>
-      <c r="AS36" s="5"/>
-      <c r="AT36" s="12" t="inlineStr">
+      <c r="AS36" s="6"/>
+      <c r="AT36" s="14" t="inlineStr">
         <is>
           <t>（必ずご記入ください）</t>
         </is>
       </c>
-      <c r="AU36" s="6"/>
-      <c r="AV36" s="6"/>
-      <c r="AW36" s="6"/>
-      <c r="AX36" s="6"/>
-      <c r="AY36" s="6"/>
-      <c r="AZ36" s="6"/>
-      <c r="BA36" s="7"/>
+      <c r="AU36" s="7"/>
+      <c r="AV36" s="7"/>
+      <c r="AW36" s="7"/>
+      <c r="AX36" s="7"/>
+      <c r="AY36" s="7"/>
+      <c r="AZ36" s="7"/>
+      <c r="BA36" s="15"/>
     </row>
     <row r="37">
-      <c r="AN37" s="10"/>
+      <c r="AN37" s="11"/>
       <c r="AO37" s="2"/>
-      <c r="AP37" s="13" t="inlineStr">
+      <c r="AP37" s="16" t="inlineStr">
         <is>
           <t>〒</t>
         </is>
@@ -1829,7 +2274,7 @@
       <c r="AT37" s="2"/>
       <c r="AU37" s="2"/>
       <c r="AV37" s="2"/>
-      <c r="AW37" s="14" t="inlineStr">
+      <c r="AW37" s="17" t="inlineStr">
         <is>
           <t>－</t>
         </is>
@@ -1842,178 +2287,247 @@
       <c r="BC37" s="2"/>
       <c r="BD37" s="2"/>
       <c r="BE37" s="3"/>
+      <c r="BF37" s="11"/>
     </row>
     <row r="38">
-      <c r="AN38" s="15" t="inlineStr">
+      <c r="AN38" s="18" t="inlineStr">
         <is>
           <t>住</t>
         </is>
       </c>
-      <c r="AS38" s="16" t="inlineStr">
+      <c r="AS38" s="19" t="inlineStr">
         <is>
           <t>所</t>
         </is>
       </c>
-      <c r="BE38" s="17"/>
+      <c r="BE38" s="20"/>
+      <c r="BF38" s="4"/>
     </row>
     <row r="39">
-      <c r="B39" s="18" t="inlineStr">
+      <c r="B39" s="21" t="inlineStr">
         <is>
           <t>支払票NO</t>
         </is>
       </c>
-      <c r="C39" s="19"/>
-      <c r="D39" s="20"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="20"/>
-      <c r="AN39" s="15" t="inlineStr">
+      <c r="C39" s="7"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
+      <c r="H39" s="7"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="11"/>
+      <c r="AN39" s="18" t="inlineStr">
         <is>
           <t>取引先名</t>
         </is>
       </c>
-      <c r="BE39" s="17"/>
+      <c r="BE39" s="20"/>
+      <c r="BF39" s="4"/>
     </row>
     <row r="40">
-      <c r="AN40" s="23"/>
-      <c r="BE40" s="22" t="inlineStr">
+      <c r="B40" s="11"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="11"/>
+      <c r="AN40" s="4"/>
+      <c r="BE40" s="23" t="inlineStr">
         <is>
           <t>印</t>
         </is>
       </c>
+      <c r="BF40" s="4"/>
     </row>
     <row r="41">
-      <c r="B41" s="11" t="inlineStr">
+      <c r="B41" s="13" t="inlineStr">
         <is>
           <t>※請求書ご提出にあたってのお願い</t>
         </is>
       </c>
-      <c r="AN41" s="15" t="inlineStr">
+      <c r="AN41" s="18" t="inlineStr">
         <is>
           <t>代表者名</t>
         </is>
       </c>
-      <c r="BE41" s="17"/>
+      <c r="BE41" s="20"/>
+      <c r="BF41" s="4"/>
     </row>
     <row r="42">
-      <c r="B42" s="11" t="inlineStr">
+      <c r="B42" s="13" t="inlineStr">
         <is>
           <t>１．記入項目について</t>
         </is>
       </c>
-      <c r="E42" s="11" t="inlineStr">
+      <c r="E42" s="22" t="inlineStr">
         <is>
           <t>注文書が発行されている場合</t>
         </is>
       </c>
-      <c r="O42" s="11" t="inlineStr">
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2"/>
+      <c r="N42" s="2"/>
+      <c r="O42" s="17" t="inlineStr">
         <is>
           <t>・・・</t>
         </is>
       </c>
-      <c r="R42" s="11" t="inlineStr">
+      <c r="P42" s="2"/>
+      <c r="Q42" s="2"/>
+      <c r="R42" s="17" t="inlineStr">
         <is>
           <t>太枠内と灰色の部分</t>
         </is>
       </c>
-      <c r="AN42" s="23"/>
-      <c r="AT42" s="11" t="inlineStr">
+      <c r="S42" s="2"/>
+      <c r="T42" s="2"/>
+      <c r="U42" s="2"/>
+      <c r="V42" s="2"/>
+      <c r="W42" s="2"/>
+      <c r="X42" s="2"/>
+      <c r="Y42" s="2"/>
+      <c r="Z42" s="2"/>
+      <c r="AA42" s="2"/>
+      <c r="AB42" s="2"/>
+      <c r="AC42" s="2"/>
+      <c r="AD42" s="2"/>
+      <c r="AE42" s="2"/>
+      <c r="AF42" s="11"/>
+      <c r="AN42" s="4"/>
+      <c r="AT42" s="13" t="inlineStr">
         <is>
           <t>電話</t>
         </is>
       </c>
-      <c r="AX42" s="11" t="inlineStr">
+      <c r="AX42" s="13" t="inlineStr">
         <is>
           <t>－</t>
         </is>
       </c>
-      <c r="BB42" s="11" t="inlineStr">
+      <c r="BB42" s="13" t="inlineStr">
         <is>
           <t>－</t>
         </is>
       </c>
-      <c r="BE42" s="17"/>
+      <c r="BE42" s="20"/>
+      <c r="BF42" s="4"/>
     </row>
     <row r="43">
-      <c r="B43" s="11" t="inlineStr">
+      <c r="B43" s="13" t="inlineStr">
         <is>
           <t>２．納入品目を記入しきれない場合は、総額を記入し御社の請求明細書を添付してください。</t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
+      <c r="E43" s="22" t="inlineStr">
         <is>
           <t>注文書が発行されていない場合・・・</t>
         </is>
       </c>
-      <c r="R43" s="11" t="inlineStr">
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
+      <c r="M43" s="2"/>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+      <c r="P43" s="2"/>
+      <c r="Q43" s="2"/>
+      <c r="R43" s="17" t="inlineStr">
         <is>
           <t>太枠内のみ</t>
         </is>
       </c>
-      <c r="AN43" s="15" t="inlineStr">
+      <c r="S43" s="2"/>
+      <c r="T43" s="2"/>
+      <c r="U43" s="2"/>
+      <c r="V43" s="2"/>
+      <c r="W43" s="2"/>
+      <c r="X43" s="2"/>
+      <c r="Y43" s="2"/>
+      <c r="Z43" s="2"/>
+      <c r="AA43" s="2"/>
+      <c r="AB43" s="2"/>
+      <c r="AC43" s="2"/>
+      <c r="AD43" s="2"/>
+      <c r="AE43" s="2"/>
+      <c r="AF43" s="11"/>
+      <c r="AN43" s="18" t="inlineStr">
         <is>
           <t>登振込録先番情号報Ｔ銀行</t>
         </is>
       </c>
-      <c r="BA43" s="16" t="inlineStr">
+      <c r="BA43" s="19" t="inlineStr">
         <is>
           <t>支店</t>
         </is>
       </c>
-      <c r="BE43" s="17"/>
+      <c r="BE43" s="20"/>
+      <c r="BF43" s="4"/>
     </row>
     <row r="44">
-      <c r="B44" s="11" t="inlineStr">
+      <c r="B44" s="13" t="inlineStr">
         <is>
           <t>３．軽油税、産廃税については、「工事名（品名）」欄に個別に明記してください。</t>
         </is>
       </c>
-      <c r="AN44" s="5"/>
-      <c r="AO44" s="6"/>
-      <c r="AP44" s="6"/>
-      <c r="AQ44" s="6"/>
-      <c r="AR44" s="6"/>
-      <c r="AS44" s="6"/>
-      <c r="AT44" s="24" t="inlineStr">
+      <c r="AN44" s="34"/>
+      <c r="AO44" s="35"/>
+      <c r="AP44" s="35"/>
+      <c r="AQ44" s="35"/>
+      <c r="AR44" s="35"/>
+      <c r="AS44" s="35"/>
+      <c r="AT44" s="43" t="inlineStr">
         <is>
           <t>口座名義(ｶﾀｶﾅ)：預金</t>
         </is>
       </c>
-      <c r="AU44" s="6"/>
-      <c r="AV44" s="6"/>
-      <c r="AW44" s="6"/>
-      <c r="AX44" s="6"/>
-      <c r="AY44" s="6"/>
-      <c r="AZ44" s="24" t="inlineStr">
+      <c r="AU44" s="35"/>
+      <c r="AV44" s="35"/>
+      <c r="AW44" s="35"/>
+      <c r="AX44" s="35"/>
+      <c r="AY44" s="35"/>
+      <c r="AZ44" s="43" t="inlineStr">
         <is>
           <t>口座番号：</t>
         </is>
       </c>
-      <c r="BA44" s="6"/>
-      <c r="BB44" s="6"/>
-      <c r="BC44" s="6"/>
-      <c r="BD44" s="6"/>
-      <c r="BE44" s="7"/>
+      <c r="BA44" s="35"/>
+      <c r="BB44" s="35"/>
+      <c r="BC44" s="35"/>
+      <c r="BD44" s="35"/>
+      <c r="BE44" s="36"/>
+      <c r="BF44" s="4"/>
     </row>
     <row r="45">
-      <c r="B45" s="10"/>
+      <c r="B45" s="11"/>
       <c r="C45" s="2"/>
       <c r="D45" s="3"/>
-      <c r="E45" s="21"/>
-      <c r="F45" s="26" t="inlineStr">
+      <c r="E45" s="6"/>
+      <c r="F45" s="27" t="inlineStr">
         <is>
           <t>科目コード</t>
         </is>
       </c>
-      <c r="G45" s="19"/>
-      <c r="H45" s="19"/>
-      <c r="I45" s="20"/>
-      <c r="J45" s="10"/>
+      <c r="G45" s="7"/>
+      <c r="H45" s="7"/>
+      <c r="I45" s="8"/>
+      <c r="J45" s="11"/>
       <c r="K45" s="2"/>
       <c r="L45" s="3"/>
-      <c r="M45" s="10"/>
+      <c r="M45" s="11"/>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" s="2"/>
@@ -2032,126 +2546,131 @@
       <c r="AC45" s="2"/>
       <c r="AD45" s="2"/>
       <c r="AE45" s="3"/>
-      <c r="AF45" s="10"/>
+      <c r="AF45" s="11"/>
       <c r="AG45" s="2"/>
       <c r="AH45" s="3"/>
-      <c r="AI45" s="10"/>
+      <c r="AI45" s="11"/>
       <c r="AJ45" s="2"/>
       <c r="AK45" s="2"/>
       <c r="AL45" s="2"/>
       <c r="AM45" s="3"/>
-      <c r="AN45" s="10"/>
+      <c r="AN45" s="11"/>
       <c r="AO45" s="2"/>
       <c r="AP45" s="2"/>
       <c r="AQ45" s="2"/>
       <c r="AR45" s="3"/>
-      <c r="AS45" s="21"/>
-      <c r="AT45" s="19"/>
-      <c r="AU45" s="19"/>
-      <c r="AV45" s="19"/>
-      <c r="AW45" s="26" t="inlineStr">
+      <c r="AS45" s="6"/>
+      <c r="AT45" s="6"/>
+      <c r="AU45" s="7"/>
+      <c r="AV45" s="7"/>
+      <c r="AW45" s="27" t="inlineStr">
         <is>
           <t>今回請求額</t>
         </is>
       </c>
-      <c r="AX45" s="19"/>
-      <c r="AY45" s="19"/>
-      <c r="AZ45" s="19"/>
-      <c r="BA45" s="19"/>
-      <c r="BB45" s="19"/>
-      <c r="BC45" s="20"/>
-      <c r="BD45" s="37" t="inlineStr">
+      <c r="AX45" s="7"/>
+      <c r="AY45" s="7"/>
+      <c r="AZ45" s="7"/>
+      <c r="BA45" s="7"/>
+      <c r="BB45" s="7"/>
+      <c r="BC45" s="8"/>
+      <c r="BD45" s="44" t="inlineStr">
         <is>
           <t>グリーン産業</t>
         </is>
       </c>
       <c r="BE45" s="2"/>
-      <c r="BF45" s="3"/>
+      <c r="BF45" s="12"/>
+      <c r="BG45" s="4"/>
     </row>
     <row r="46">
-      <c r="B46" s="38" t="inlineStr">
+      <c r="B46" s="45" t="inlineStr">
         <is>
           <t>工事NO</t>
         </is>
       </c>
-      <c r="C46" s="6"/>
-      <c r="D46" s="7"/>
-      <c r="F46" s="29" t="inlineStr">
+      <c r="C46" s="35"/>
+      <c r="D46" s="36"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="27" t="inlineStr">
         <is>
           <t>科目名</t>
         </is>
       </c>
-      <c r="J46" s="5"/>
-      <c r="K46" s="39" t="inlineStr">
+      <c r="G46" s="7"/>
+      <c r="H46" s="7"/>
+      <c r="I46" s="8"/>
+      <c r="J46" s="6"/>
+      <c r="K46" s="46" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="L46" s="7"/>
-      <c r="M46" s="5"/>
-      <c r="N46" s="6"/>
-      <c r="O46" s="6"/>
-      <c r="P46" s="6"/>
-      <c r="Q46" s="6"/>
-      <c r="R46" s="6"/>
-      <c r="S46" s="6"/>
-      <c r="T46" s="6"/>
-      <c r="U46" s="39" t="inlineStr">
+      <c r="L46" s="36"/>
+      <c r="M46" s="34"/>
+      <c r="N46" s="35"/>
+      <c r="O46" s="35"/>
+      <c r="P46" s="35"/>
+      <c r="Q46" s="35"/>
+      <c r="R46" s="35"/>
+      <c r="S46" s="35"/>
+      <c r="T46" s="35"/>
+      <c r="U46" s="46" t="inlineStr">
         <is>
           <t>工事名（品名）</t>
         </is>
       </c>
-      <c r="V46" s="6"/>
-      <c r="W46" s="6"/>
-      <c r="X46" s="6"/>
-      <c r="Y46" s="6"/>
-      <c r="Z46" s="6"/>
-      <c r="AA46" s="6"/>
-      <c r="AB46" s="6"/>
-      <c r="AC46" s="6"/>
-      <c r="AD46" s="6"/>
-      <c r="AE46" s="7"/>
-      <c r="AF46" s="5"/>
-      <c r="AG46" s="40" t="inlineStr">
+      <c r="V46" s="35"/>
+      <c r="W46" s="35"/>
+      <c r="X46" s="35"/>
+      <c r="Y46" s="35"/>
+      <c r="Z46" s="35"/>
+      <c r="AA46" s="35"/>
+      <c r="AB46" s="35"/>
+      <c r="AC46" s="35"/>
+      <c r="AD46" s="35"/>
+      <c r="AE46" s="36"/>
+      <c r="AF46" s="34"/>
+      <c r="AG46" s="47" t="inlineStr">
         <is>
           <t>内訳NO</t>
         </is>
       </c>
-      <c r="AH46" s="7"/>
-      <c r="AI46" s="38" t="inlineStr">
+      <c r="AH46" s="36"/>
+      <c r="AI46" s="45" t="inlineStr">
         <is>
           <t>現在注文金額</t>
         </is>
       </c>
-      <c r="AJ46" s="6"/>
-      <c r="AK46" s="6"/>
-      <c r="AL46" s="6"/>
-      <c r="AM46" s="7"/>
-      <c r="AN46" s="38" t="inlineStr">
+      <c r="AJ46" s="35"/>
+      <c r="AK46" s="35"/>
+      <c r="AL46" s="35"/>
+      <c r="AM46" s="36"/>
+      <c r="AN46" s="45" t="inlineStr">
         <is>
           <t>前回迄の支払額</t>
         </is>
       </c>
-      <c r="AO46" s="6"/>
-      <c r="AP46" s="6"/>
-      <c r="AQ46" s="6"/>
-      <c r="AR46" s="7"/>
+      <c r="AO46" s="35"/>
+      <c r="AP46" s="35"/>
+      <c r="AQ46" s="35"/>
+      <c r="AR46" s="36"/>
       <c r="AS46" s="32" t="inlineStr">
         <is>
           <t>（税抜金額）</t>
         </is>
       </c>
-      <c r="AT46" s="19"/>
+      <c r="AT46" s="6"/>
       <c r="AU46" s="33" t="inlineStr">
         <is>
           <t>（税抜金額）</t>
         </is>
       </c>
-      <c r="AV46" s="19"/>
-      <c r="AW46" s="19"/>
-      <c r="AX46" s="19"/>
-      <c r="AY46" s="19"/>
-      <c r="AZ46" s="20"/>
+      <c r="AV46" s="7"/>
+      <c r="AW46" s="7"/>
+      <c r="AX46" s="7"/>
+      <c r="AY46" s="7"/>
+      <c r="AZ46" s="8"/>
       <c r="BA46" s="32" t="inlineStr">
         <is>
           <t>税率</t>
@@ -2162,97 +2681,157 @@
           <t>税率</t>
         </is>
       </c>
-      <c r="BC46" s="20"/>
-      <c r="BD46" s="41" t="inlineStr">
+      <c r="BC46" s="8"/>
+      <c r="BD46" s="29" t="inlineStr">
         <is>
           <t>担当者確認欄</t>
         </is>
       </c>
-      <c r="BE46" s="6"/>
-      <c r="BF46" s="7"/>
+      <c r="BE46" s="35"/>
+      <c r="BF46" s="36"/>
+      <c r="BG46" s="4"/>
     </row>
     <row r="47">
-      <c r="B47" s="21"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="20"/>
-      <c r="E47" s="21"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="19"/>
-      <c r="H47" s="19"/>
-      <c r="I47" s="20"/>
-      <c r="J47" s="21"/>
-      <c r="K47" s="19"/>
-      <c r="L47" s="20"/>
-      <c r="M47" s="21"/>
-      <c r="N47" s="19"/>
-      <c r="O47" s="19"/>
-      <c r="P47" s="19"/>
-      <c r="Q47" s="19"/>
-      <c r="R47" s="19"/>
-      <c r="S47" s="19"/>
-      <c r="T47" s="19"/>
-      <c r="U47" s="19"/>
-      <c r="V47" s="19"/>
-      <c r="W47" s="19"/>
-      <c r="X47" s="19"/>
-      <c r="Y47" s="19"/>
-      <c r="Z47" s="19"/>
-      <c r="AA47" s="19"/>
-      <c r="AB47" s="19"/>
-      <c r="AC47" s="19"/>
-      <c r="AD47" s="19"/>
-      <c r="AE47" s="20"/>
-      <c r="AF47" s="21"/>
-      <c r="AG47" s="19"/>
-      <c r="AH47" s="20"/>
-      <c r="AI47" s="42" t="inlineStr">
+      <c r="B47" s="6"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="7"/>
+      <c r="H47" s="7"/>
+      <c r="I47" s="8"/>
+      <c r="J47" s="6"/>
+      <c r="K47" s="7"/>
+      <c r="L47" s="8"/>
+      <c r="M47" s="6"/>
+      <c r="N47" s="7"/>
+      <c r="O47" s="7"/>
+      <c r="P47" s="7"/>
+      <c r="Q47" s="7"/>
+      <c r="R47" s="7"/>
+      <c r="S47" s="7"/>
+      <c r="T47" s="7"/>
+      <c r="U47" s="7"/>
+      <c r="V47" s="7"/>
+      <c r="W47" s="7"/>
+      <c r="X47" s="7"/>
+      <c r="Y47" s="7"/>
+      <c r="Z47" s="7"/>
+      <c r="AA47" s="7"/>
+      <c r="AB47" s="7"/>
+      <c r="AC47" s="7"/>
+      <c r="AD47" s="7"/>
+      <c r="AE47" s="8"/>
+      <c r="AF47" s="6"/>
+      <c r="AG47" s="7"/>
+      <c r="AH47" s="8"/>
+      <c r="AI47" s="37" t="inlineStr">
         <is>
           <t>（税抜金額）</t>
         </is>
       </c>
-      <c r="AJ47" s="19"/>
-      <c r="AK47" s="19"/>
-      <c r="AL47" s="19"/>
-      <c r="AM47" s="20"/>
-      <c r="AN47" s="21"/>
+      <c r="AJ47" s="7"/>
+      <c r="AK47" s="7"/>
+      <c r="AL47" s="7"/>
+      <c r="AM47" s="8"/>
+      <c r="AN47" s="6"/>
       <c r="AO47" s="33" t="inlineStr">
         <is>
           <t>（税抜金額）</t>
         </is>
       </c>
-      <c r="AP47" s="19"/>
-      <c r="AQ47" s="19"/>
-      <c r="AR47" s="20"/>
-      <c r="BD47" s="21"/>
-      <c r="BE47" s="19"/>
-      <c r="BF47" s="20"/>
+      <c r="AP47" s="7"/>
+      <c r="AQ47" s="7"/>
+      <c r="AR47" s="8"/>
+      <c r="AS47" s="6"/>
+      <c r="AT47" s="6"/>
+      <c r="AU47" s="7"/>
+      <c r="AV47" s="7"/>
+      <c r="AW47" s="7"/>
+      <c r="AX47" s="7"/>
+      <c r="AY47" s="7"/>
+      <c r="AZ47" s="8"/>
+      <c r="BA47" s="6"/>
+      <c r="BB47" s="7"/>
+      <c r="BC47" s="8"/>
+      <c r="BD47" s="6"/>
+      <c r="BE47" s="7"/>
+      <c r="BF47" s="8"/>
+      <c r="BG47" s="4"/>
     </row>
     <row r="48">
-      <c r="AS48" s="21"/>
-      <c r="AT48" s="19"/>
-      <c r="AU48" s="19"/>
-      <c r="AV48" s="19"/>
-      <c r="AW48" s="19"/>
-      <c r="AX48" s="19"/>
-      <c r="AY48" s="19"/>
-      <c r="AZ48" s="20"/>
-      <c r="BA48" s="21"/>
-      <c r="BB48" s="19"/>
-      <c r="BC48" s="20"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7"/>
+      <c r="H48" s="7"/>
+      <c r="I48" s="8"/>
+      <c r="J48" s="6"/>
+      <c r="K48" s="7"/>
+      <c r="L48" s="8"/>
+      <c r="M48" s="6"/>
+      <c r="N48" s="7"/>
+      <c r="O48" s="7"/>
+      <c r="P48" s="7"/>
+      <c r="Q48" s="7"/>
+      <c r="R48" s="7"/>
+      <c r="S48" s="7"/>
+      <c r="T48" s="7"/>
+      <c r="U48" s="7"/>
+      <c r="V48" s="7"/>
+      <c r="W48" s="7"/>
+      <c r="X48" s="7"/>
+      <c r="Y48" s="7"/>
+      <c r="Z48" s="7"/>
+      <c r="AA48" s="7"/>
+      <c r="AB48" s="7"/>
+      <c r="AC48" s="7"/>
+      <c r="AD48" s="7"/>
+      <c r="AE48" s="8"/>
+      <c r="AF48" s="6"/>
+      <c r="AG48" s="7"/>
+      <c r="AH48" s="8"/>
+      <c r="AI48" s="6"/>
+      <c r="AJ48" s="7"/>
+      <c r="AK48" s="7"/>
+      <c r="AL48" s="7"/>
+      <c r="AM48" s="8"/>
+      <c r="AN48" s="6"/>
+      <c r="AO48" s="7"/>
+      <c r="AP48" s="7"/>
+      <c r="AQ48" s="7"/>
+      <c r="AR48" s="8"/>
+      <c r="AS48" s="6"/>
+      <c r="AT48" s="6"/>
+      <c r="AU48" s="7"/>
+      <c r="AV48" s="7"/>
+      <c r="AW48" s="7"/>
+      <c r="AX48" s="7"/>
+      <c r="AY48" s="7"/>
+      <c r="AZ48" s="8"/>
+      <c r="BA48" s="6"/>
+      <c r="BB48" s="7"/>
+      <c r="BC48" s="8"/>
+      <c r="BD48" s="6"/>
+      <c r="BE48" s="7"/>
+      <c r="BF48" s="8"/>
+      <c r="BG48" s="4"/>
     </row>
     <row r="49">
-      <c r="B49" s="10"/>
+      <c r="B49" s="11"/>
       <c r="C49" s="2"/>
       <c r="D49" s="3"/>
-      <c r="E49" s="21"/>
-      <c r="F49" s="19"/>
-      <c r="G49" s="19"/>
-      <c r="H49" s="19"/>
-      <c r="I49" s="20"/>
-      <c r="J49" s="10"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="7"/>
+      <c r="H49" s="7"/>
+      <c r="I49" s="8"/>
+      <c r="J49" s="11"/>
       <c r="K49" s="2"/>
       <c r="L49" s="3"/>
-      <c r="M49" s="10"/>
+      <c r="M49" s="11"/>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" s="2"/>
@@ -2271,160 +2850,228 @@
       <c r="AC49" s="2"/>
       <c r="AD49" s="2"/>
       <c r="AE49" s="3"/>
-      <c r="AF49" s="10"/>
+      <c r="AF49" s="11"/>
       <c r="AG49" s="2"/>
       <c r="AH49" s="3"/>
-      <c r="AI49" s="10"/>
+      <c r="AI49" s="11"/>
       <c r="AJ49" s="2"/>
       <c r="AK49" s="2"/>
       <c r="AL49" s="2"/>
       <c r="AM49" s="3"/>
-      <c r="AN49" s="10"/>
+      <c r="AN49" s="11"/>
       <c r="AO49" s="2"/>
       <c r="AP49" s="2"/>
       <c r="AQ49" s="2"/>
       <c r="AR49" s="3"/>
-      <c r="AS49" s="10"/>
-      <c r="AT49" s="2"/>
+      <c r="AS49" s="11"/>
+      <c r="AT49" s="11"/>
       <c r="AU49" s="2"/>
       <c r="AV49" s="2"/>
       <c r="AW49" s="2"/>
       <c r="AX49" s="2"/>
       <c r="AY49" s="2"/>
       <c r="AZ49" s="3"/>
-      <c r="BA49" s="10"/>
+      <c r="BA49" s="11"/>
       <c r="BB49" s="2"/>
       <c r="BC49" s="3"/>
-      <c r="BD49" s="10"/>
+      <c r="BD49" s="11"/>
       <c r="BE49" s="2"/>
       <c r="BF49" s="3"/>
+      <c r="BG49" s="4"/>
     </row>
     <row r="50">
-      <c r="B50" s="5"/>
-      <c r="C50" s="6"/>
-      <c r="D50" s="7"/>
-      <c r="J50" s="5"/>
-      <c r="K50" s="6"/>
-      <c r="L50" s="7"/>
-      <c r="M50" s="5"/>
-      <c r="N50" s="6"/>
-      <c r="O50" s="6"/>
-      <c r="P50" s="6"/>
-      <c r="Q50" s="6"/>
-      <c r="R50" s="6"/>
-      <c r="S50" s="6"/>
-      <c r="T50" s="6"/>
-      <c r="U50" s="6"/>
-      <c r="V50" s="6"/>
-      <c r="W50" s="6"/>
-      <c r="X50" s="6"/>
-      <c r="Y50" s="6"/>
-      <c r="Z50" s="6"/>
-      <c r="AA50" s="6"/>
-      <c r="AB50" s="6"/>
-      <c r="AC50" s="6"/>
-      <c r="AD50" s="6"/>
-      <c r="AE50" s="7"/>
-      <c r="AF50" s="5"/>
-      <c r="AG50" s="6"/>
-      <c r="AH50" s="7"/>
-      <c r="AI50" s="5"/>
-      <c r="AJ50" s="6"/>
-      <c r="AK50" s="6"/>
-      <c r="AL50" s="6"/>
-      <c r="AM50" s="7"/>
-      <c r="AN50" s="5"/>
-      <c r="AO50" s="6"/>
-      <c r="AP50" s="6"/>
-      <c r="AQ50" s="6"/>
-      <c r="AR50" s="7"/>
-      <c r="AS50" s="5"/>
-      <c r="AT50" s="6"/>
-      <c r="AU50" s="6"/>
-      <c r="AV50" s="6"/>
-      <c r="AW50" s="6"/>
-      <c r="AX50" s="6"/>
-      <c r="AY50" s="6"/>
-      <c r="AZ50" s="7"/>
-      <c r="BA50" s="5"/>
-      <c r="BB50" s="6"/>
-      <c r="BC50" s="7"/>
-      <c r="BD50" s="5"/>
-      <c r="BE50" s="6"/>
-      <c r="BF50" s="7"/>
+      <c r="B50" s="34"/>
+      <c r="C50" s="35"/>
+      <c r="D50" s="36"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="7"/>
+      <c r="G50" s="7"/>
+      <c r="H50" s="7"/>
+      <c r="I50" s="8"/>
+      <c r="J50" s="6"/>
+      <c r="K50" s="35"/>
+      <c r="L50" s="36"/>
+      <c r="M50" s="34"/>
+      <c r="N50" s="35"/>
+      <c r="O50" s="35"/>
+      <c r="P50" s="35"/>
+      <c r="Q50" s="35"/>
+      <c r="R50" s="35"/>
+      <c r="S50" s="35"/>
+      <c r="T50" s="35"/>
+      <c r="U50" s="35"/>
+      <c r="V50" s="35"/>
+      <c r="W50" s="35"/>
+      <c r="X50" s="35"/>
+      <c r="Y50" s="35"/>
+      <c r="Z50" s="35"/>
+      <c r="AA50" s="35"/>
+      <c r="AB50" s="35"/>
+      <c r="AC50" s="35"/>
+      <c r="AD50" s="35"/>
+      <c r="AE50" s="36"/>
+      <c r="AF50" s="34"/>
+      <c r="AG50" s="35"/>
+      <c r="AH50" s="36"/>
+      <c r="AI50" s="34"/>
+      <c r="AJ50" s="35"/>
+      <c r="AK50" s="35"/>
+      <c r="AL50" s="35"/>
+      <c r="AM50" s="36"/>
+      <c r="AN50" s="34"/>
+      <c r="AO50" s="35"/>
+      <c r="AP50" s="35"/>
+      <c r="AQ50" s="35"/>
+      <c r="AR50" s="36"/>
+      <c r="AS50" s="34"/>
+      <c r="AT50" s="34"/>
+      <c r="AU50" s="35"/>
+      <c r="AV50" s="35"/>
+      <c r="AW50" s="35"/>
+      <c r="AX50" s="35"/>
+      <c r="AY50" s="35"/>
+      <c r="AZ50" s="36"/>
+      <c r="BA50" s="34"/>
+      <c r="BB50" s="35"/>
+      <c r="BC50" s="36"/>
+      <c r="BD50" s="34"/>
+      <c r="BE50" s="35"/>
+      <c r="BF50" s="36"/>
+      <c r="BG50" s="4"/>
     </row>
     <row r="51">
-      <c r="B51" s="21"/>
-      <c r="C51" s="19"/>
-      <c r="D51" s="20"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="19"/>
-      <c r="G51" s="19"/>
-      <c r="H51" s="19"/>
-      <c r="I51" s="20"/>
-      <c r="J51" s="21"/>
-      <c r="K51" s="19"/>
-      <c r="L51" s="20"/>
-      <c r="M51" s="21"/>
-      <c r="N51" s="19"/>
-      <c r="O51" s="19"/>
-      <c r="P51" s="19"/>
-      <c r="Q51" s="19"/>
-      <c r="R51" s="19"/>
-      <c r="S51" s="19"/>
-      <c r="T51" s="19"/>
-      <c r="U51" s="19"/>
-      <c r="V51" s="19"/>
-      <c r="W51" s="19"/>
-      <c r="X51" s="19"/>
-      <c r="Y51" s="19"/>
-      <c r="Z51" s="19"/>
-      <c r="AA51" s="19"/>
-      <c r="AB51" s="19"/>
-      <c r="AC51" s="19"/>
-      <c r="AD51" s="19"/>
-      <c r="AE51" s="20"/>
-      <c r="AF51" s="21"/>
-      <c r="AG51" s="19"/>
-      <c r="AH51" s="20"/>
-      <c r="AI51" s="21"/>
-      <c r="AJ51" s="19"/>
-      <c r="AK51" s="19"/>
-      <c r="AL51" s="19"/>
-      <c r="AM51" s="20"/>
-      <c r="AN51" s="21"/>
-      <c r="AO51" s="19"/>
-      <c r="AP51" s="19"/>
-      <c r="AQ51" s="19"/>
-      <c r="AR51" s="20"/>
-      <c r="AS51" s="21"/>
-      <c r="AT51" s="19"/>
-      <c r="AU51" s="19"/>
-      <c r="AV51" s="19"/>
-      <c r="AW51" s="19"/>
-      <c r="AX51" s="19"/>
-      <c r="AY51" s="19"/>
-      <c r="AZ51" s="20"/>
-      <c r="BA51" s="21"/>
-      <c r="BB51" s="19"/>
-      <c r="BC51" s="20"/>
-      <c r="BD51" s="21"/>
-      <c r="BE51" s="19"/>
-      <c r="BF51" s="20"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="7"/>
+      <c r="G51" s="7"/>
+      <c r="H51" s="7"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="6"/>
+      <c r="K51" s="7"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="6"/>
+      <c r="N51" s="7"/>
+      <c r="O51" s="7"/>
+      <c r="P51" s="7"/>
+      <c r="Q51" s="7"/>
+      <c r="R51" s="7"/>
+      <c r="S51" s="7"/>
+      <c r="T51" s="7"/>
+      <c r="U51" s="7"/>
+      <c r="V51" s="7"/>
+      <c r="W51" s="7"/>
+      <c r="X51" s="7"/>
+      <c r="Y51" s="7"/>
+      <c r="Z51" s="7"/>
+      <c r="AA51" s="7"/>
+      <c r="AB51" s="7"/>
+      <c r="AC51" s="7"/>
+      <c r="AD51" s="7"/>
+      <c r="AE51" s="8"/>
+      <c r="AF51" s="6"/>
+      <c r="AG51" s="7"/>
+      <c r="AH51" s="8"/>
+      <c r="AI51" s="6"/>
+      <c r="AJ51" s="7"/>
+      <c r="AK51" s="7"/>
+      <c r="AL51" s="7"/>
+      <c r="AM51" s="8"/>
+      <c r="AN51" s="6"/>
+      <c r="AO51" s="7"/>
+      <c r="AP51" s="7"/>
+      <c r="AQ51" s="7"/>
+      <c r="AR51" s="8"/>
+      <c r="AS51" s="6"/>
+      <c r="AT51" s="6"/>
+      <c r="AU51" s="7"/>
+      <c r="AV51" s="7"/>
+      <c r="AW51" s="7"/>
+      <c r="AX51" s="7"/>
+      <c r="AY51" s="7"/>
+      <c r="AZ51" s="8"/>
+      <c r="BA51" s="6"/>
+      <c r="BB51" s="7"/>
+      <c r="BC51" s="8"/>
+      <c r="BD51" s="6"/>
+      <c r="BE51" s="7"/>
+      <c r="BF51" s="8"/>
+      <c r="BG51" s="4"/>
+    </row>
+    <row r="52">
+      <c r="B52" s="6"/>
+      <c r="C52" s="7"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="7"/>
+      <c r="G52" s="7"/>
+      <c r="H52" s="7"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="6"/>
+      <c r="K52" s="7"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="6"/>
+      <c r="N52" s="7"/>
+      <c r="O52" s="7"/>
+      <c r="P52" s="7"/>
+      <c r="Q52" s="7"/>
+      <c r="R52" s="7"/>
+      <c r="S52" s="7"/>
+      <c r="T52" s="7"/>
+      <c r="U52" s="7"/>
+      <c r="V52" s="7"/>
+      <c r="W52" s="7"/>
+      <c r="X52" s="7"/>
+      <c r="Y52" s="7"/>
+      <c r="Z52" s="7"/>
+      <c r="AA52" s="7"/>
+      <c r="AB52" s="7"/>
+      <c r="AC52" s="7"/>
+      <c r="AD52" s="7"/>
+      <c r="AE52" s="8"/>
+      <c r="AF52" s="6"/>
+      <c r="AG52" s="7"/>
+      <c r="AH52" s="8"/>
+      <c r="AI52" s="6"/>
+      <c r="AJ52" s="7"/>
+      <c r="AK52" s="7"/>
+      <c r="AL52" s="7"/>
+      <c r="AM52" s="8"/>
+      <c r="AN52" s="6"/>
+      <c r="AO52" s="7"/>
+      <c r="AP52" s="7"/>
+      <c r="AQ52" s="7"/>
+      <c r="AR52" s="8"/>
+      <c r="AS52" s="6"/>
+      <c r="AT52" s="6"/>
+      <c r="AU52" s="7"/>
+      <c r="AV52" s="7"/>
+      <c r="AW52" s="7"/>
+      <c r="AX52" s="7"/>
+      <c r="AY52" s="7"/>
+      <c r="AZ52" s="8"/>
+      <c r="BA52" s="6"/>
+      <c r="BB52" s="7"/>
+      <c r="BC52" s="8"/>
+      <c r="BD52" s="6"/>
+      <c r="BE52" s="7"/>
+      <c r="BF52" s="8"/>
+      <c r="BG52" s="4"/>
     </row>
     <row r="53">
-      <c r="B53" s="10"/>
+      <c r="B53" s="11"/>
       <c r="C53" s="2"/>
       <c r="D53" s="3"/>
-      <c r="E53" s="21"/>
-      <c r="F53" s="19"/>
-      <c r="G53" s="19"/>
-      <c r="H53" s="19"/>
-      <c r="I53" s="20"/>
-      <c r="J53" s="10"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="7"/>
+      <c r="G53" s="7"/>
+      <c r="H53" s="7"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="11"/>
       <c r="K53" s="2"/>
       <c r="L53" s="3"/>
-      <c r="M53" s="10"/>
+      <c r="M53" s="11"/>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" s="2"/>
@@ -2443,231 +3090,297 @@
       <c r="AC53" s="2"/>
       <c r="AD53" s="2"/>
       <c r="AE53" s="3"/>
-      <c r="AF53" s="10"/>
+      <c r="AF53" s="11"/>
       <c r="AG53" s="2"/>
       <c r="AH53" s="3"/>
-      <c r="AI53" s="10"/>
+      <c r="AI53" s="11"/>
       <c r="AJ53" s="2"/>
       <c r="AK53" s="2"/>
       <c r="AL53" s="2"/>
       <c r="AM53" s="3"/>
-      <c r="AN53" s="10"/>
+      <c r="AN53" s="11"/>
       <c r="AO53" s="2"/>
       <c r="AP53" s="2"/>
       <c r="AQ53" s="2"/>
       <c r="AR53" s="3"/>
-      <c r="AS53" s="10"/>
-      <c r="AT53" s="2"/>
+      <c r="AS53" s="11"/>
+      <c r="AT53" s="11"/>
       <c r="AU53" s="2"/>
       <c r="AV53" s="2"/>
       <c r="AW53" s="2"/>
       <c r="AX53" s="2"/>
       <c r="AY53" s="2"/>
       <c r="AZ53" s="3"/>
-      <c r="BA53" s="10"/>
+      <c r="BA53" s="11"/>
       <c r="BB53" s="2"/>
       <c r="BC53" s="3"/>
-      <c r="BD53" s="10"/>
+      <c r="BD53" s="11"/>
       <c r="BE53" s="2"/>
       <c r="BF53" s="3"/>
+      <c r="BG53" s="4"/>
     </row>
     <row r="54">
-      <c r="B54" s="5"/>
-      <c r="C54" s="6"/>
-      <c r="D54" s="7"/>
-      <c r="J54" s="5"/>
-      <c r="K54" s="6"/>
-      <c r="L54" s="7"/>
-      <c r="M54" s="5"/>
-      <c r="N54" s="6"/>
-      <c r="O54" s="6"/>
-      <c r="P54" s="6"/>
-      <c r="Q54" s="6"/>
-      <c r="R54" s="6"/>
-      <c r="S54" s="6"/>
-      <c r="T54" s="6"/>
-      <c r="U54" s="6"/>
-      <c r="V54" s="6"/>
-      <c r="W54" s="6"/>
-      <c r="X54" s="6"/>
-      <c r="Y54" s="6"/>
-      <c r="Z54" s="6"/>
-      <c r="AA54" s="6"/>
-      <c r="AB54" s="6"/>
-      <c r="AC54" s="6"/>
-      <c r="AD54" s="6"/>
-      <c r="AE54" s="7"/>
-      <c r="AF54" s="5"/>
-      <c r="AG54" s="6"/>
-      <c r="AH54" s="7"/>
-      <c r="AI54" s="5"/>
-      <c r="AJ54" s="6"/>
-      <c r="AK54" s="6"/>
-      <c r="AL54" s="6"/>
-      <c r="AM54" s="7"/>
-      <c r="AN54" s="5"/>
-      <c r="AO54" s="6"/>
-      <c r="AP54" s="6"/>
-      <c r="AQ54" s="6"/>
-      <c r="AR54" s="7"/>
-      <c r="AS54" s="5"/>
+      <c r="B54" s="6"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="7"/>
+      <c r="G54" s="7"/>
+      <c r="H54" s="7"/>
+      <c r="I54" s="8"/>
+      <c r="J54" s="6"/>
+      <c r="K54" s="7"/>
+      <c r="L54" s="8"/>
+      <c r="M54" s="6"/>
+      <c r="N54" s="7"/>
+      <c r="O54" s="7"/>
+      <c r="P54" s="7"/>
+      <c r="Q54" s="7"/>
+      <c r="R54" s="7"/>
+      <c r="S54" s="7"/>
+      <c r="T54" s="7"/>
+      <c r="U54" s="7"/>
+      <c r="V54" s="7"/>
+      <c r="W54" s="7"/>
+      <c r="X54" s="7"/>
+      <c r="Y54" s="7"/>
+      <c r="Z54" s="7"/>
+      <c r="AA54" s="7"/>
+      <c r="AB54" s="7"/>
+      <c r="AC54" s="7"/>
+      <c r="AD54" s="7"/>
+      <c r="AE54" s="8"/>
+      <c r="AF54" s="6"/>
+      <c r="AG54" s="7"/>
+      <c r="AH54" s="8"/>
+      <c r="AI54" s="6"/>
+      <c r="AJ54" s="7"/>
+      <c r="AK54" s="7"/>
+      <c r="AL54" s="7"/>
+      <c r="AM54" s="8"/>
+      <c r="AN54" s="6"/>
+      <c r="AO54" s="7"/>
+      <c r="AP54" s="7"/>
+      <c r="AQ54" s="7"/>
+      <c r="AR54" s="8"/>
+      <c r="AS54" s="6"/>
       <c r="AT54" s="6"/>
-      <c r="AU54" s="6"/>
-      <c r="AV54" s="6"/>
-      <c r="AW54" s="6"/>
-      <c r="AX54" s="6"/>
-      <c r="AY54" s="6"/>
-      <c r="AZ54" s="7"/>
-      <c r="BA54" s="5"/>
-      <c r="BB54" s="6"/>
-      <c r="BC54" s="7"/>
-      <c r="BD54" s="5"/>
-      <c r="BE54" s="6"/>
-      <c r="BF54" s="7"/>
+      <c r="AU54" s="7"/>
+      <c r="AV54" s="7"/>
+      <c r="AW54" s="7"/>
+      <c r="AX54" s="7"/>
+      <c r="AY54" s="7"/>
+      <c r="AZ54" s="8"/>
+      <c r="BA54" s="6"/>
+      <c r="BB54" s="7"/>
+      <c r="BC54" s="8"/>
+      <c r="BD54" s="6"/>
+      <c r="BE54" s="7"/>
+      <c r="BF54" s="8"/>
+      <c r="BG54" s="4"/>
     </row>
     <row r="55">
-      <c r="B55" s="21"/>
-      <c r="C55" s="19"/>
-      <c r="D55" s="19"/>
-      <c r="E55" s="19"/>
-      <c r="F55" s="19"/>
-      <c r="G55" s="19"/>
-      <c r="H55" s="19"/>
-      <c r="I55" s="19"/>
-      <c r="J55" s="19"/>
-      <c r="K55" s="19"/>
-      <c r="L55" s="19"/>
-      <c r="M55" s="19"/>
-      <c r="N55" s="19"/>
-      <c r="O55" s="19"/>
-      <c r="P55" s="19"/>
-      <c r="Q55" s="19"/>
-      <c r="R55" s="19"/>
-      <c r="S55" s="19"/>
-      <c r="T55" s="19"/>
-      <c r="U55" s="19"/>
-      <c r="V55" s="19"/>
-      <c r="W55" s="19"/>
-      <c r="X55" s="19"/>
-      <c r="Y55" s="19"/>
-      <c r="Z55" s="19"/>
-      <c r="AA55" s="19"/>
-      <c r="AB55" s="19"/>
-      <c r="AC55" s="19"/>
-      <c r="AD55" s="19"/>
-      <c r="AE55" s="19"/>
-      <c r="AF55" s="19"/>
-      <c r="AG55" s="19"/>
-      <c r="AH55" s="19"/>
-      <c r="AI55" s="19"/>
-      <c r="AJ55" s="19"/>
-      <c r="AK55" s="19"/>
-      <c r="AL55" s="19"/>
-      <c r="AM55" s="20"/>
-      <c r="AN55" s="21"/>
+      <c r="B55" s="6"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="7"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
+      <c r="J55" s="6"/>
+      <c r="K55" s="7"/>
+      <c r="L55" s="7"/>
+      <c r="M55" s="7"/>
+      <c r="N55" s="7"/>
+      <c r="O55" s="7"/>
+      <c r="P55" s="7"/>
+      <c r="Q55" s="7"/>
+      <c r="R55" s="7"/>
+      <c r="S55" s="7"/>
+      <c r="T55" s="7"/>
+      <c r="U55" s="7"/>
+      <c r="V55" s="7"/>
+      <c r="W55" s="7"/>
+      <c r="X55" s="7"/>
+      <c r="Y55" s="7"/>
+      <c r="Z55" s="7"/>
+      <c r="AA55" s="7"/>
+      <c r="AB55" s="7"/>
+      <c r="AC55" s="7"/>
+      <c r="AD55" s="7"/>
+      <c r="AE55" s="7"/>
+      <c r="AF55" s="7"/>
+      <c r="AG55" s="7"/>
+      <c r="AH55" s="7"/>
+      <c r="AI55" s="6"/>
+      <c r="AJ55" s="7"/>
+      <c r="AK55" s="7"/>
+      <c r="AL55" s="7"/>
+      <c r="AM55" s="8"/>
+      <c r="AN55" s="6"/>
       <c r="AO55" s="33" t="inlineStr">
         <is>
           <t>（税抜金額）</t>
         </is>
       </c>
-      <c r="AP55" s="19"/>
-      <c r="AQ55" s="19"/>
-      <c r="AR55" s="20"/>
-      <c r="AS55" s="21"/>
-      <c r="AT55" s="33" t="inlineStr">
+      <c r="AP55" s="7"/>
+      <c r="AQ55" s="7"/>
+      <c r="AR55" s="8"/>
+      <c r="AS55" s="6"/>
+      <c r="AT55" s="37" t="inlineStr">
         <is>
           <t>(消費税)</t>
         </is>
       </c>
-      <c r="AU55" s="19"/>
-      <c r="AV55" s="19"/>
-      <c r="AW55" s="20"/>
-      <c r="AX55" s="21"/>
+      <c r="AU55" s="7"/>
+      <c r="AV55" s="7"/>
+      <c r="AW55" s="8"/>
+      <c r="AX55" s="6"/>
       <c r="AY55" s="33" t="inlineStr">
         <is>
           <t>(税込金額)</t>
         </is>
       </c>
-      <c r="AZ55" s="19"/>
-      <c r="BA55" s="19"/>
-      <c r="BB55" s="19"/>
-      <c r="BC55" s="20"/>
-      <c r="BD55" s="21"/>
-      <c r="BE55" s="19"/>
-      <c r="BF55" s="20"/>
+      <c r="AZ55" s="7"/>
+      <c r="BA55" s="6"/>
+      <c r="BB55" s="7"/>
+      <c r="BC55" s="8"/>
+      <c r="BD55" s="6"/>
+      <c r="BE55" s="7"/>
+      <c r="BF55" s="8"/>
+      <c r="BG55" s="4"/>
     </row>
     <row r="56">
-      <c r="AH56" s="9" t="inlineStr">
+      <c r="B56" s="6"/>
+      <c r="C56" s="7"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="7"/>
+      <c r="F56" s="7"/>
+      <c r="G56" s="7"/>
+      <c r="H56" s="7"/>
+      <c r="I56" s="7"/>
+      <c r="J56" s="7"/>
+      <c r="K56" s="7"/>
+      <c r="L56" s="7"/>
+      <c r="M56" s="7"/>
+      <c r="N56" s="7"/>
+      <c r="O56" s="7"/>
+      <c r="P56" s="7"/>
+      <c r="Q56" s="7"/>
+      <c r="R56" s="7"/>
+      <c r="S56" s="7"/>
+      <c r="T56" s="7"/>
+      <c r="U56" s="7"/>
+      <c r="V56" s="7"/>
+      <c r="W56" s="7"/>
+      <c r="X56" s="7"/>
+      <c r="Y56" s="7"/>
+      <c r="Z56" s="7"/>
+      <c r="AA56" s="7"/>
+      <c r="AB56" s="7"/>
+      <c r="AC56" s="7"/>
+      <c r="AD56" s="7"/>
+      <c r="AE56" s="7"/>
+      <c r="AF56" s="7"/>
+      <c r="AG56" s="7"/>
+      <c r="AH56" s="33" t="inlineStr">
         <is>
           <t>非・不課税小計</t>
         </is>
       </c>
+      <c r="AI56" s="7"/>
+      <c r="AJ56" s="7"/>
+      <c r="AK56" s="7"/>
+      <c r="AL56" s="7"/>
+      <c r="AM56" s="8"/>
+      <c r="AN56" s="6"/>
+      <c r="AO56" s="7"/>
+      <c r="AP56" s="7"/>
+      <c r="AQ56" s="7"/>
+      <c r="AR56" s="8"/>
+      <c r="AS56" s="6"/>
+      <c r="AT56" s="7"/>
+      <c r="AU56" s="7"/>
+      <c r="AV56" s="7"/>
+      <c r="AW56" s="8"/>
+      <c r="AX56" s="6"/>
+      <c r="AY56" s="7"/>
+      <c r="AZ56" s="7"/>
+      <c r="BA56" s="7"/>
+      <c r="BB56" s="7"/>
+      <c r="BC56" s="8"/>
+      <c r="BD56" s="6"/>
+      <c r="BE56" s="7"/>
+      <c r="BF56" s="8"/>
+      <c r="BG56" s="4"/>
     </row>
     <row r="57">
-      <c r="B57" s="21"/>
-      <c r="C57" s="19"/>
-      <c r="D57" s="19"/>
-      <c r="E57" s="19"/>
-      <c r="F57" s="19"/>
-      <c r="G57" s="19"/>
-      <c r="H57" s="19"/>
-      <c r="I57" s="19"/>
-      <c r="J57" s="19"/>
-      <c r="K57" s="19"/>
-      <c r="L57" s="19"/>
-      <c r="M57" s="19"/>
-      <c r="N57" s="19"/>
-      <c r="O57" s="19"/>
-      <c r="P57" s="19"/>
-      <c r="Q57" s="19"/>
-      <c r="R57" s="19"/>
-      <c r="S57" s="19"/>
-      <c r="T57" s="19"/>
-      <c r="U57" s="19"/>
-      <c r="V57" s="19"/>
-      <c r="W57" s="19"/>
-      <c r="X57" s="19"/>
-      <c r="Y57" s="19"/>
-      <c r="Z57" s="19"/>
-      <c r="AA57" s="19"/>
-      <c r="AB57" s="19"/>
-      <c r="AC57" s="19"/>
-      <c r="AD57" s="19"/>
-      <c r="AE57" s="19"/>
-      <c r="AF57" s="19"/>
-      <c r="AG57" s="19"/>
-      <c r="AH57" s="19"/>
-      <c r="AI57" s="19"/>
-      <c r="AJ57" s="19"/>
+      <c r="B57" s="6"/>
+      <c r="C57" s="7"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="7"/>
+      <c r="G57" s="7"/>
+      <c r="H57" s="7"/>
+      <c r="I57" s="7"/>
+      <c r="J57" s="7"/>
+      <c r="K57" s="7"/>
+      <c r="L57" s="7"/>
+      <c r="M57" s="7"/>
+      <c r="N57" s="7"/>
+      <c r="O57" s="7"/>
+      <c r="P57" s="7"/>
+      <c r="Q57" s="7"/>
+      <c r="R57" s="7"/>
+      <c r="S57" s="7"/>
+      <c r="T57" s="7"/>
+      <c r="U57" s="7"/>
+      <c r="V57" s="7"/>
+      <c r="W57" s="7"/>
+      <c r="X57" s="7"/>
+      <c r="Y57" s="7"/>
+      <c r="Z57" s="7"/>
+      <c r="AA57" s="7"/>
+      <c r="AB57" s="7"/>
+      <c r="AC57" s="7"/>
+      <c r="AD57" s="7"/>
+      <c r="AE57" s="7"/>
+      <c r="AF57" s="7"/>
+      <c r="AG57" s="7"/>
+      <c r="AH57" s="7"/>
+      <c r="AI57" s="7"/>
+      <c r="AJ57" s="7"/>
       <c r="AK57" s="33" t="inlineStr">
         <is>
           <t>8%小計</t>
         </is>
       </c>
-      <c r="AL57" s="19"/>
-      <c r="AM57" s="20"/>
-      <c r="AN57" s="21"/>
-      <c r="AO57" s="19"/>
-      <c r="AP57" s="19"/>
-      <c r="AQ57" s="19"/>
-      <c r="AR57" s="20"/>
-      <c r="AS57" s="21"/>
-      <c r="AT57" s="19"/>
-      <c r="AU57" s="19"/>
-      <c r="AV57" s="19"/>
-      <c r="AW57" s="20"/>
-      <c r="AX57" s="21"/>
-      <c r="AY57" s="19"/>
-      <c r="AZ57" s="19"/>
-      <c r="BA57" s="19"/>
-      <c r="BB57" s="19"/>
-      <c r="BC57" s="20"/>
-      <c r="BD57" s="21"/>
-      <c r="BE57" s="19"/>
-      <c r="BF57" s="20"/>
+      <c r="AL57" s="7"/>
+      <c r="AM57" s="8"/>
+      <c r="AN57" s="6"/>
+      <c r="AO57" s="7"/>
+      <c r="AP57" s="7"/>
+      <c r="AQ57" s="7"/>
+      <c r="AR57" s="8"/>
+      <c r="AS57" s="6"/>
+      <c r="AT57" s="7"/>
+      <c r="AU57" s="7"/>
+      <c r="AV57" s="7"/>
+      <c r="AW57" s="8"/>
+      <c r="AX57" s="6"/>
+      <c r="AY57" s="7"/>
+      <c r="AZ57" s="7"/>
+      <c r="BA57" s="7"/>
+      <c r="BB57" s="7"/>
+      <c r="BC57" s="8"/>
+      <c r="BD57" s="6"/>
+      <c r="BE57" s="7"/>
+      <c r="BF57" s="8"/>
+      <c r="BG57" s="4"/>
     </row>
     <row r="58">
-      <c r="B58" s="10"/>
+      <c r="B58" s="11"/>
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -2705,166 +3418,225 @@
       <c r="AK58" s="2"/>
       <c r="AL58" s="2"/>
       <c r="AM58" s="3"/>
-      <c r="AN58" s="10"/>
+      <c r="AN58" s="11"/>
       <c r="AO58" s="2"/>
       <c r="AP58" s="2"/>
       <c r="AQ58" s="2"/>
       <c r="AR58" s="3"/>
-      <c r="AS58" s="10"/>
+      <c r="AS58" s="11"/>
       <c r="AT58" s="2"/>
       <c r="AU58" s="2"/>
       <c r="AV58" s="2"/>
       <c r="AW58" s="3"/>
-      <c r="AX58" s="10"/>
+      <c r="AX58" s="11"/>
       <c r="AY58" s="2"/>
       <c r="AZ58" s="2"/>
       <c r="BA58" s="2"/>
       <c r="BB58" s="2"/>
       <c r="BC58" s="3"/>
-      <c r="BD58" s="10"/>
+      <c r="BD58" s="11"/>
       <c r="BE58" s="2"/>
       <c r="BF58" s="3"/>
+      <c r="BG58" s="4"/>
     </row>
     <row r="59">
-      <c r="B59" s="5"/>
-      <c r="C59" s="6"/>
-      <c r="D59" s="6"/>
-      <c r="E59" s="6"/>
-      <c r="F59" s="6"/>
-      <c r="G59" s="6"/>
-      <c r="H59" s="6"/>
-      <c r="I59" s="6"/>
-      <c r="J59" s="6"/>
-      <c r="K59" s="6"/>
-      <c r="L59" s="6"/>
-      <c r="M59" s="6"/>
-      <c r="N59" s="6"/>
-      <c r="O59" s="6"/>
-      <c r="P59" s="6"/>
-      <c r="Q59" s="6"/>
-      <c r="R59" s="6"/>
-      <c r="S59" s="6"/>
-      <c r="T59" s="6"/>
-      <c r="U59" s="6"/>
-      <c r="V59" s="6"/>
-      <c r="W59" s="6"/>
-      <c r="X59" s="6"/>
-      <c r="Y59" s="6"/>
-      <c r="Z59" s="6"/>
-      <c r="AA59" s="6"/>
-      <c r="AB59" s="6"/>
-      <c r="AC59" s="6"/>
-      <c r="AD59" s="6"/>
-      <c r="AE59" s="6"/>
-      <c r="AF59" s="6"/>
-      <c r="AG59" s="6"/>
-      <c r="AH59" s="6"/>
-      <c r="AI59" s="6"/>
-      <c r="AJ59" s="34" t="inlineStr">
+      <c r="B59" s="34"/>
+      <c r="C59" s="35"/>
+      <c r="D59" s="35"/>
+      <c r="E59" s="35"/>
+      <c r="F59" s="35"/>
+      <c r="G59" s="35"/>
+      <c r="H59" s="35"/>
+      <c r="I59" s="35"/>
+      <c r="J59" s="35"/>
+      <c r="K59" s="35"/>
+      <c r="L59" s="35"/>
+      <c r="M59" s="35"/>
+      <c r="N59" s="35"/>
+      <c r="O59" s="35"/>
+      <c r="P59" s="35"/>
+      <c r="Q59" s="35"/>
+      <c r="R59" s="35"/>
+      <c r="S59" s="35"/>
+      <c r="T59" s="35"/>
+      <c r="U59" s="35"/>
+      <c r="V59" s="35"/>
+      <c r="W59" s="35"/>
+      <c r="X59" s="35"/>
+      <c r="Y59" s="35"/>
+      <c r="Z59" s="35"/>
+      <c r="AA59" s="35"/>
+      <c r="AB59" s="35"/>
+      <c r="AC59" s="35"/>
+      <c r="AD59" s="35"/>
+      <c r="AE59" s="35"/>
+      <c r="AF59" s="35"/>
+      <c r="AG59" s="35"/>
+      <c r="AH59" s="35"/>
+      <c r="AI59" s="35"/>
+      <c r="AJ59" s="38" t="inlineStr">
         <is>
           <t>10%小計</t>
         </is>
       </c>
-      <c r="AK59" s="6"/>
-      <c r="AL59" s="6"/>
-      <c r="AM59" s="7"/>
-      <c r="AN59" s="5"/>
-      <c r="AO59" s="6"/>
-      <c r="AP59" s="6"/>
-      <c r="AQ59" s="6"/>
-      <c r="AR59" s="7"/>
-      <c r="AS59" s="5"/>
-      <c r="AT59" s="6"/>
-      <c r="AU59" s="6"/>
-      <c r="AV59" s="6"/>
-      <c r="AW59" s="7"/>
-      <c r="AX59" s="5"/>
-      <c r="AY59" s="6"/>
-      <c r="AZ59" s="6"/>
-      <c r="BA59" s="6"/>
-      <c r="BB59" s="6"/>
-      <c r="BC59" s="7"/>
-      <c r="BD59" s="5"/>
-      <c r="BE59" s="6"/>
-      <c r="BF59" s="7"/>
+      <c r="AK59" s="35"/>
+      <c r="AL59" s="35"/>
+      <c r="AM59" s="36"/>
+      <c r="AN59" s="34"/>
+      <c r="AO59" s="35"/>
+      <c r="AP59" s="35"/>
+      <c r="AQ59" s="35"/>
+      <c r="AR59" s="36"/>
+      <c r="AS59" s="34"/>
+      <c r="AT59" s="35"/>
+      <c r="AU59" s="35"/>
+      <c r="AV59" s="35"/>
+      <c r="AW59" s="36"/>
+      <c r="AX59" s="34"/>
+      <c r="AY59" s="35"/>
+      <c r="AZ59" s="35"/>
+      <c r="BA59" s="35"/>
+      <c r="BB59" s="35"/>
+      <c r="BC59" s="36"/>
+      <c r="BD59" s="34"/>
+      <c r="BE59" s="35"/>
+      <c r="BF59" s="36"/>
+      <c r="BG59" s="4"/>
     </row>
     <row r="60">
-      <c r="B60" s="21"/>
-      <c r="C60" s="19"/>
-      <c r="D60" s="19"/>
-      <c r="E60" s="19"/>
-      <c r="F60" s="19"/>
-      <c r="G60" s="19"/>
-      <c r="H60" s="19"/>
-      <c r="I60" s="19"/>
-      <c r="J60" s="19"/>
-      <c r="K60" s="19"/>
-      <c r="L60" s="19"/>
-      <c r="M60" s="19"/>
-      <c r="N60" s="19"/>
-      <c r="O60" s="19"/>
-      <c r="P60" s="19"/>
-      <c r="Q60" s="19"/>
-      <c r="R60" s="19"/>
-      <c r="S60" s="19"/>
-      <c r="T60" s="19"/>
-      <c r="U60" s="19"/>
-      <c r="V60" s="19"/>
-      <c r="W60" s="19"/>
-      <c r="X60" s="19"/>
-      <c r="Y60" s="19"/>
-      <c r="Z60" s="19"/>
-      <c r="AA60" s="19"/>
-      <c r="AB60" s="19"/>
-      <c r="AC60" s="19"/>
-      <c r="AD60" s="19"/>
-      <c r="AE60" s="19"/>
-      <c r="AF60" s="19"/>
-      <c r="AG60" s="19"/>
-      <c r="AH60" s="19"/>
-      <c r="AI60" s="19"/>
-      <c r="AJ60" s="19"/>
+      <c r="B60" s="6"/>
+      <c r="C60" s="7"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="7"/>
+      <c r="G60" s="7"/>
+      <c r="H60" s="7"/>
+      <c r="I60" s="7"/>
+      <c r="J60" s="7"/>
+      <c r="K60" s="7"/>
+      <c r="L60" s="7"/>
+      <c r="M60" s="7"/>
+      <c r="N60" s="7"/>
+      <c r="O60" s="7"/>
+      <c r="P60" s="7"/>
+      <c r="Q60" s="7"/>
+      <c r="R60" s="7"/>
+      <c r="S60" s="7"/>
+      <c r="T60" s="7"/>
+      <c r="U60" s="7"/>
+      <c r="V60" s="7"/>
+      <c r="W60" s="7"/>
+      <c r="X60" s="7"/>
+      <c r="Y60" s="7"/>
+      <c r="Z60" s="7"/>
+      <c r="AA60" s="7"/>
+      <c r="AB60" s="7"/>
+      <c r="AC60" s="7"/>
+      <c r="AD60" s="7"/>
+      <c r="AE60" s="7"/>
+      <c r="AF60" s="7"/>
+      <c r="AG60" s="7"/>
+      <c r="AH60" s="7"/>
+      <c r="AI60" s="7"/>
+      <c r="AJ60" s="7"/>
       <c r="AK60" s="33" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="AL60" s="19"/>
-      <c r="AM60" s="20"/>
-      <c r="AN60" s="21"/>
-      <c r="AO60" s="19"/>
-      <c r="AP60" s="19"/>
-      <c r="AQ60" s="19"/>
-      <c r="AR60" s="20"/>
-      <c r="AS60" s="21"/>
-      <c r="AT60" s="19"/>
-      <c r="AU60" s="19"/>
-      <c r="AV60" s="19"/>
-      <c r="AW60" s="20"/>
-      <c r="AX60" s="21"/>
-      <c r="AY60" s="19"/>
-      <c r="AZ60" s="19"/>
-      <c r="BA60" s="19"/>
-      <c r="BB60" s="19"/>
-      <c r="BC60" s="20"/>
-      <c r="BD60" s="21"/>
-      <c r="BE60" s="19"/>
-      <c r="BF60" s="20"/>
+      <c r="AL60" s="7"/>
+      <c r="AM60" s="8"/>
+      <c r="AN60" s="6"/>
+      <c r="AO60" s="7"/>
+      <c r="AP60" s="7"/>
+      <c r="AQ60" s="7"/>
+      <c r="AR60" s="8"/>
+      <c r="AS60" s="6"/>
+      <c r="AT60" s="7"/>
+      <c r="AU60" s="7"/>
+      <c r="AV60" s="7"/>
+      <c r="AW60" s="8"/>
+      <c r="AX60" s="6"/>
+      <c r="AY60" s="7"/>
+      <c r="AZ60" s="7"/>
+      <c r="BA60" s="7"/>
+      <c r="BB60" s="7"/>
+      <c r="BC60" s="8"/>
+      <c r="BD60" s="6"/>
+      <c r="BE60" s="7"/>
+      <c r="BF60" s="8"/>
+      <c r="BG60" s="4"/>
     </row>
     <row r="61">
-      <c r="B61" s="16" t="inlineStr">
+      <c r="B61" s="39" t="inlineStr">
         <is>
           <t>※提出部数</t>
         </is>
       </c>
-      <c r="F61" s="16" t="inlineStr">
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="40" t="inlineStr">
         <is>
           <t>1部（白黒で構いません）・・・毎月５日必着</t>
         </is>
       </c>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
+      <c r="J61" s="2"/>
+      <c r="K61" s="2"/>
+      <c r="L61" s="2"/>
+      <c r="M61" s="2"/>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" s="2"/>
+      <c r="Q61" s="2"/>
+      <c r="R61" s="2"/>
+      <c r="S61" s="2"/>
+      <c r="T61" s="2"/>
+      <c r="U61" s="2"/>
+      <c r="V61" s="2"/>
+      <c r="W61" s="2"/>
+      <c r="X61" s="2"/>
+      <c r="Y61" s="2"/>
+      <c r="Z61" s="2"/>
+      <c r="AA61" s="2"/>
+      <c r="AB61" s="2"/>
+      <c r="AC61" s="2"/>
+      <c r="AD61" s="2"/>
+      <c r="AE61" s="2"/>
+      <c r="AF61" s="2"/>
+      <c r="AG61" s="2"/>
+      <c r="AH61" s="2"/>
+      <c r="AI61" s="2"/>
+      <c r="AJ61" s="2"/>
+      <c r="AK61" s="2"/>
+      <c r="AL61" s="2"/>
+      <c r="AM61" s="2"/>
+      <c r="AN61" s="11"/>
+      <c r="AO61" s="2"/>
+      <c r="AP61" s="2"/>
+      <c r="AQ61" s="2"/>
+      <c r="AR61" s="2"/>
+      <c r="AS61" s="11"/>
+      <c r="AT61" s="2"/>
+      <c r="AU61" s="2"/>
+      <c r="AV61" s="2"/>
+      <c r="AW61" s="2"/>
+      <c r="AX61" s="11"/>
+      <c r="AY61" s="2"/>
+      <c r="AZ61" s="2"/>
+      <c r="BA61" s="2"/>
+      <c r="BB61" s="2"/>
+      <c r="BC61" s="2"/>
+      <c r="BD61" s="11"/>
+      <c r="BE61" s="2"/>
+      <c r="BF61" s="2"/>
+      <c r="BG61" s="4"/>
     </row>
     <row r="62">
-      <c r="B62" s="16" t="inlineStr">
+      <c r="B62" s="19" t="inlineStr">
         <is>
           <t>※毎年１２月のみ２０日締切（２５日必着）翌月末日支払いとさせていただきます。</t>
         </is>

--- a/data/out/test0/seikyuusyo202505_Python版_2pt.xlsx
+++ b/data/out/test0/seikyuusyo202505_Python版_2pt.xlsx
@@ -28,60 +28,60 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="MS PGothic"/>
+      <name val="MSゴシック"/>
       <sz val="7.2"/>
     </font>
     <font>
-      <name val="MS PGothic"/>
+      <name val="MSゴシック"/>
       <sz val="13"/>
     </font>
     <font>
-      <name val="MS PGothic"/>
+      <name val="MSゴシック"/>
       <sz val="10.1"/>
     </font>
     <font>
-      <name val="MS PGothic"/>
+      <name val="MSゴシック"/>
       <sz val="8.6"/>
     </font>
     <font>
-      <name val="MS Mincho"/>
+      <name val="MS明朝"/>
       <sz val="7.9"/>
     </font>
     <font>
-      <name val="MS Mincho"/>
+      <name val="MS明朝"/>
       <color rgb="00FF0000"/>
       <sz val="7.2"/>
     </font>
     <font>
-      <name val="MS Mincho"/>
+      <name val="MS明朝"/>
       <sz val="8.6"/>
     </font>
     <font>
-      <name val="MS Mincho"/>
+      <name val="MS明朝"/>
       <sz val="11.5"/>
     </font>
     <font>
-      <name val="MS PGothic"/>
+      <name val="MSゴシック"/>
       <sz val="6.5"/>
     </font>
     <font>
-      <name val="MS PGothic"/>
+      <name val="MSゴシック"/>
       <sz val="7.9"/>
     </font>
     <font>
-      <name val="MS PGothic"/>
+      <name val="MSゴシック"/>
       <sz val="7"/>
     </font>
     <font>
-      <name val="MS Gothic"/>
+      <name val="MSゴシック"/>
       <sz val="6"/>
     </font>
     <font>
-      <name val="MS PMincho"/>
+      <name val="MS明朝"/>
       <sz val="5.1"/>
     </font>
     <font>
-      <name val="MS PMincho"/>
+      <name val="MS明朝"/>
       <sz val="7.6"/>
     </font>
   </fonts>

--- a/data/out/test0/seikyuusyo202505_Python版_2pt.xlsx
+++ b/data/out/test0/seikyuusyo202505_Python版_2pt.xlsx
@@ -28,60 +28,60 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="MSゴシック"/>
+      <name val="MS ゴシック"/>
       <sz val="7.2"/>
     </font>
     <font>
-      <name val="MSゴシック"/>
+      <name val="MS ゴシック"/>
       <sz val="13"/>
     </font>
     <font>
-      <name val="MSゴシック"/>
+      <name val="MS ゴシック"/>
       <sz val="10.1"/>
     </font>
     <font>
-      <name val="MSゴシック"/>
+      <name val="MS ゴシック"/>
       <sz val="8.6"/>
     </font>
     <font>
-      <name val="MS明朝"/>
+      <name val="MS 明朝"/>
       <sz val="7.9"/>
     </font>
     <font>
-      <name val="MS明朝"/>
+      <name val="MS 明朝"/>
       <color rgb="00FF0000"/>
       <sz val="7.2"/>
     </font>
     <font>
-      <name val="MS明朝"/>
+      <name val="MS 明朝"/>
       <sz val="8.6"/>
     </font>
     <font>
-      <name val="MS明朝"/>
+      <name val="MS 明朝"/>
       <sz val="11.5"/>
     </font>
     <font>
-      <name val="MSゴシック"/>
+      <name val="MS ゴシック"/>
       <sz val="6.5"/>
     </font>
     <font>
-      <name val="MSゴシック"/>
+      <name val="MS ゴシック"/>
       <sz val="7.9"/>
     </font>
     <font>
-      <name val="MSゴシック"/>
+      <name val="MS ゴシック"/>
       <sz val="7"/>
     </font>
     <font>
-      <name val="MSゴシック"/>
+      <name val="MS 明朝"/>
       <sz val="6"/>
     </font>
     <font>
-      <name val="MS明朝"/>
+      <name val="MS 明朝"/>
       <sz val="5.1"/>
     </font>
     <font>
-      <name val="MS明朝"/>
+      <name val="MS 明朝"/>
       <sz val="7.6"/>
     </font>
   </fonts>
